--- a/2026_연간_일별공급계획_2.xlsx
+++ b/2026_연간_일별공급계획_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\일일예측_관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2C8560-D94D-4AD5-8420-FB41CB8A18B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056957BB-6339-40CC-9D6E-39A470CFFF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="연간" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +101,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -122,7 +130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -201,6 +209,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -249,35 +266,45 @@
     <xf numFmtId="41" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -626,7 +653,7 @@
       <c r="D3" s="7">
         <v>222239.28700000001</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="24">
         <v>5221420</v>
       </c>
     </row>
@@ -641,9 +668,9 @@
         <v>2</v>
       </c>
       <c r="D4" s="7">
-        <v>234714.14800000002</v>
-      </c>
-      <c r="E4" s="10">
+        <v>234714.14799999999</v>
+      </c>
+      <c r="E4" s="24">
         <v>5514511</v>
       </c>
     </row>
@@ -660,7 +687,7 @@
       <c r="D5" s="7">
         <v>215678.46100000001</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="24">
         <v>5067276</v>
       </c>
     </row>
@@ -677,7 +704,7 @@
       <c r="D6" s="7">
         <v>223052.383</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="24">
         <v>5240523</v>
       </c>
     </row>
@@ -692,9 +719,9 @@
         <v>5</v>
       </c>
       <c r="D7" s="7">
-        <v>247058.79200000002</v>
-      </c>
-      <c r="E7" s="10">
+        <v>247058.79199999999</v>
+      </c>
+      <c r="E7" s="24">
         <v>5804544</v>
       </c>
     </row>
@@ -709,9 +736,9 @@
         <v>6</v>
       </c>
       <c r="D8" s="7">
-        <v>244242.36000000002</v>
-      </c>
-      <c r="E8" s="10">
+        <v>244242.36</v>
+      </c>
+      <c r="E8" s="24">
         <v>5738373</v>
       </c>
     </row>
@@ -728,7 +755,7 @@
       <c r="D9" s="7">
         <v>240732.91</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="24">
         <v>5655920</v>
       </c>
     </row>
@@ -745,7 +772,7 @@
       <c r="D10" s="7">
         <v>255078.853</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="24">
         <v>5992972</v>
       </c>
     </row>
@@ -762,7 +789,7 @@
       <c r="D11" s="7">
         <v>247122.62</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="24">
         <v>5806043</v>
       </c>
     </row>
@@ -779,7 +806,7 @@
       <c r="D12" s="7">
         <v>224087.94899999999</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="24">
         <v>5264853</v>
       </c>
     </row>
@@ -794,9 +821,9 @@
         <v>11</v>
       </c>
       <c r="D13" s="7">
-        <v>224781.54200000002</v>
-      </c>
-      <c r="E13" s="10">
+        <v>224781.54199999999</v>
+      </c>
+      <c r="E13" s="24">
         <v>5281149</v>
       </c>
     </row>
@@ -813,7 +840,7 @@
       <c r="D14" s="7">
         <v>251814.35200000001</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="24">
         <v>5916274</v>
       </c>
     </row>
@@ -830,7 +857,7 @@
       <c r="D15" s="7">
         <v>247136.269</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="24">
         <v>5806364</v>
       </c>
     </row>
@@ -847,7 +874,7 @@
       <c r="D16" s="7">
         <v>242494.166</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="24">
         <v>5697300</v>
       </c>
     </row>
@@ -862,9 +889,9 @@
         <v>15</v>
       </c>
       <c r="D17" s="7">
-        <v>247809.69400000002</v>
-      </c>
-      <c r="E17" s="10">
+        <v>247809.69399999999</v>
+      </c>
+      <c r="E17" s="24">
         <v>5822186</v>
       </c>
     </row>
@@ -881,7 +908,7 @@
       <c r="D18" s="7">
         <v>240132.731</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="24">
         <v>5641819</v>
       </c>
     </row>
@@ -898,7 +925,7 @@
       <c r="D19" s="7">
         <v>226707.46</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="24">
         <v>5326398</v>
       </c>
     </row>
@@ -915,7 +942,7 @@
       <c r="D20" s="7">
         <v>198856.948</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="24">
         <v>4672061</v>
       </c>
     </row>
@@ -930,9 +957,9 @@
         <v>19</v>
       </c>
       <c r="D21" s="7">
-        <v>232772.77300000002</v>
-      </c>
-      <c r="E21" s="10">
+        <v>232772.77299999999</v>
+      </c>
+      <c r="E21" s="24">
         <v>5468900</v>
       </c>
     </row>
@@ -949,7 +976,7 @@
       <c r="D22" s="7">
         <v>240300.875</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="24">
         <v>5645769</v>
       </c>
     </row>
@@ -966,7 +993,7 @@
       <c r="D23" s="7">
         <v>253225.878</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="24">
         <v>5949437</v>
       </c>
     </row>
@@ -983,7 +1010,7 @@
       <c r="D24" s="7">
         <v>272060.95699999999</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="24">
         <v>6391959</v>
       </c>
     </row>
@@ -998,9 +1025,9 @@
         <v>23</v>
       </c>
       <c r="D25" s="7">
-        <v>261050.58000000002</v>
-      </c>
-      <c r="E25" s="10">
+        <v>261050.58</v>
+      </c>
+      <c r="E25" s="24">
         <v>6133275</v>
       </c>
     </row>
@@ -1017,7 +1044,7 @@
       <c r="D26" s="7">
         <v>242159.02100000001</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="24">
         <v>5689426</v>
       </c>
     </row>
@@ -1034,7 +1061,7 @@
       <c r="D27" s="7">
         <v>213985.36499999999</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="24">
         <v>5027497</v>
       </c>
     </row>
@@ -1049,9 +1076,9 @@
         <v>26</v>
       </c>
       <c r="D28" s="7">
-        <v>234919.48500000002</v>
-      </c>
-      <c r="E28" s="10">
+        <v>234919.48499999999</v>
+      </c>
+      <c r="E28" s="24">
         <v>5519336</v>
       </c>
     </row>
@@ -1068,7 +1095,7 @@
       <c r="D29" s="15">
         <v>307655.80599999998</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="24">
         <v>7228245</v>
       </c>
     </row>
@@ -1083,9 +1110,9 @@
         <v>28</v>
       </c>
       <c r="D30" s="7">
-        <v>282282.98600000003</v>
-      </c>
-      <c r="E30" s="10">
+        <v>282282.98599999998</v>
+      </c>
+      <c r="E30" s="24">
         <v>6632121</v>
       </c>
     </row>
@@ -1102,7 +1129,7 @@
       <c r="D31" s="7">
         <v>252978.125</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="24">
         <v>5943616</v>
       </c>
     </row>
@@ -1119,7 +1146,7 @@
       <c r="D32" s="7">
         <v>230074.56599999999</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="24">
         <v>5405506</v>
       </c>
     </row>
@@ -1136,7 +1163,7 @@
       <c r="D33" s="7">
         <v>227158.223</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="24">
         <v>5336988</v>
       </c>
     </row>
@@ -1151,10 +1178,10 @@
         <v>1</v>
       </c>
       <c r="D34" s="15">
-        <v>189264.87900000002</v>
-      </c>
-      <c r="E34" s="16">
-        <v>4446699.692220943</v>
+        <v>189264.87899999999</v>
+      </c>
+      <c r="E34" s="24">
+        <v>4446700</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1170,8 +1197,8 @@
       <c r="D35" s="15">
         <v>216471.34400000001</v>
       </c>
-      <c r="E35" s="16">
-        <v>5085904.2830627542</v>
+      <c r="E35" s="24">
+        <v>5085904</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1187,8 +1214,8 @@
       <c r="D36" s="15">
         <v>229741.63099999999</v>
       </c>
-      <c r="E36" s="16">
-        <v>5397684.1623005895</v>
+      <c r="E36" s="24">
+        <v>5397684</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1202,10 +1229,10 @@
         <v>4</v>
       </c>
       <c r="D37" s="15">
-        <v>237677.64800000002</v>
-      </c>
-      <c r="E37" s="16">
-        <v>5584137.584286822</v>
+        <v>237677.64799999999</v>
+      </c>
+      <c r="E37" s="24">
+        <v>5584138</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1221,8 +1248,8 @@
       <c r="D38" s="15">
         <v>234830.416</v>
       </c>
-      <c r="E38" s="16">
-        <v>5517243.051476635</v>
+      <c r="E38" s="24">
+        <v>5517243</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1236,10 +1263,10 @@
         <v>6</v>
       </c>
       <c r="D39" s="15">
-        <v>242249.56484632625</v>
-      </c>
-      <c r="E39" s="16">
-        <v>5691552.8709519124</v>
+        <v>242249.565</v>
+      </c>
+      <c r="E39" s="24">
+        <v>5691553</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1253,10 +1280,10 @@
         <v>7</v>
       </c>
       <c r="D40" s="15">
-        <v>216895.49394829461</v>
-      </c>
-      <c r="E40" s="16">
-        <v>5095869.5098628998</v>
+        <v>216895.49400000001</v>
+      </c>
+      <c r="E40" s="24">
+        <v>5095870</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1270,10 +1297,10 @@
         <v>8</v>
       </c>
       <c r="D41" s="15">
-        <v>217975.6727983235</v>
-      </c>
-      <c r="E41" s="16">
-        <v>5121247.8631281508</v>
+        <v>217975.67300000001</v>
+      </c>
+      <c r="E41" s="24">
+        <v>5121248</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1287,10 +1314,10 @@
         <v>9</v>
       </c>
       <c r="D42" s="15">
-        <v>219556.15720475759</v>
-      </c>
-      <c r="E42" s="16">
-        <v>5158380.6875633197</v>
+        <v>219556.15700000001</v>
+      </c>
+      <c r="E42" s="24">
+        <v>5158381</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1304,10 +1331,10 @@
         <v>10</v>
       </c>
       <c r="D43" s="15">
-        <v>223996.4765141203</v>
-      </c>
-      <c r="E43" s="16">
-        <v>5262704.1447764561</v>
+        <v>223996.47700000001</v>
+      </c>
+      <c r="E43" s="24">
+        <v>5262704</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1321,10 +1348,10 @@
         <v>11</v>
       </c>
       <c r="D44" s="15">
-        <v>221776.31685943893</v>
-      </c>
-      <c r="E44" s="16">
-        <v>5210542.4161698874</v>
+        <v>221776.31700000001</v>
+      </c>
+      <c r="E44" s="24">
+        <v>5210542</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1338,10 +1365,10 @@
         <v>12</v>
       </c>
       <c r="D45" s="15">
-        <v>225172.5109646506</v>
-      </c>
-      <c r="E45" s="16">
-        <v>5290334.5855473196</v>
+        <v>225172.511</v>
+      </c>
+      <c r="E45" s="24">
+        <v>5290335</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1355,10 +1382,10 @@
         <v>13</v>
       </c>
       <c r="D46" s="15">
-        <v>212751.05356527548</v>
-      </c>
-      <c r="E46" s="16">
-        <v>4998497.6050860016</v>
+        <v>212751.054</v>
+      </c>
+      <c r="E46" s="24">
+        <v>4998498</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1372,78 +1399,78 @@
         <v>14</v>
       </c>
       <c r="D47" s="15">
-        <v>190838.35139130434</v>
-      </c>
-      <c r="E47" s="16">
-        <v>4483667.7722741421</v>
+        <v>190838.351</v>
+      </c>
+      <c r="E47" s="24">
+        <v>4483668</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="17">
-        <v>2026</v>
-      </c>
-      <c r="B48" s="17">
+      <c r="A48" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B48" s="16">
         <v>2</v>
       </c>
-      <c r="C48" s="17">
+      <c r="C48" s="16">
         <v>15</v>
       </c>
       <c r="D48" s="15">
-        <v>186962.31341314904</v>
-      </c>
-      <c r="E48" s="16">
-        <v>4392601.8704778571</v>
+        <v>186962.31299999999</v>
+      </c>
+      <c r="E48" s="24">
+        <v>4392602</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="17">
-        <v>2026</v>
-      </c>
-      <c r="B49" s="17">
+      <c r="A49" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B49" s="16">
         <v>2</v>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="16">
         <v>16</v>
       </c>
       <c r="D49" s="15">
-        <v>185127.00005999368</v>
-      </c>
-      <c r="E49" s="16">
-        <v>4349481.9458213393</v>
+        <v>185127</v>
+      </c>
+      <c r="E49" s="24">
+        <v>4349482</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="17">
-        <v>2026</v>
-      </c>
-      <c r="B50" s="17">
+      <c r="A50" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B50" s="16">
         <v>2</v>
       </c>
-      <c r="C50" s="17">
+      <c r="C50" s="16">
         <v>17</v>
       </c>
       <c r="D50" s="15">
-        <v>177785.74664737232</v>
-      </c>
-      <c r="E50" s="16">
-        <v>4177002.2471952708</v>
+        <v>177785.747</v>
+      </c>
+      <c r="E50" s="24">
+        <v>4177002</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="17">
-        <v>2026</v>
-      </c>
-      <c r="B51" s="17">
+      <c r="A51" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B51" s="16">
         <v>2</v>
       </c>
-      <c r="C51" s="17">
+      <c r="C51" s="16">
         <v>18</v>
       </c>
       <c r="D51" s="15">
-        <v>185127.00005999368</v>
-      </c>
-      <c r="E51" s="16">
-        <v>4349481.9458213393</v>
+        <v>185127</v>
+      </c>
+      <c r="E51" s="24">
+        <v>4349482</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1457,10 +1484,10 @@
         <v>19</v>
       </c>
       <c r="D52" s="15">
-        <v>185127.00005999368</v>
-      </c>
-      <c r="E52" s="16">
-        <v>4349481.9458213393</v>
+        <v>185127</v>
+      </c>
+      <c r="E52" s="24">
+        <v>4349482</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1474,10 +1501,10 @@
         <v>20</v>
       </c>
       <c r="D53" s="15">
-        <v>186044.65673657134</v>
-      </c>
-      <c r="E53" s="16">
-        <v>4371041.9081495972</v>
+        <v>186044.65700000001</v>
+      </c>
+      <c r="E53" s="24">
+        <v>4371042</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1491,10 +1518,10 @@
         <v>21</v>
       </c>
       <c r="D54" s="15">
-        <v>189474.35139130434</v>
-      </c>
-      <c r="E54" s="16">
-        <v>4451621.1590184988</v>
+        <v>189474.351</v>
+      </c>
+      <c r="E54" s="24">
+        <v>4451621</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1508,10 +1535,10 @@
         <v>22</v>
       </c>
       <c r="D55" s="15">
-        <v>180122.35139130434</v>
-      </c>
-      <c r="E55" s="16">
-        <v>4231899.8047906477</v>
+        <v>180122.351</v>
+      </c>
+      <c r="E55" s="24">
+        <v>4231900</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1525,10 +1552,10 @@
         <v>23</v>
       </c>
       <c r="D56" s="15">
-        <v>199065.35139130434</v>
-      </c>
-      <c r="E56" s="16">
-        <v>4676957.7189414361</v>
+        <v>199065.351</v>
+      </c>
+      <c r="E56" s="24">
+        <v>4676958</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1542,10 +1569,10 @@
         <v>24</v>
       </c>
       <c r="D57" s="15">
-        <v>202169.35139130434</v>
-      </c>
-      <c r="E57" s="16">
-        <v>4749884.9092240753</v>
+        <v>202169.351</v>
+      </c>
+      <c r="E57" s="24">
+        <v>4749885</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1559,10 +1586,10 @@
         <v>25</v>
       </c>
       <c r="D58" s="15">
-        <v>203682.35139130434</v>
-      </c>
-      <c r="E58" s="16">
-        <v>4785432.2155699627</v>
+        <v>203682.351</v>
+      </c>
+      <c r="E58" s="24">
+        <v>4785432</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1576,10 +1603,10 @@
         <v>26</v>
       </c>
       <c r="D59" s="15">
-        <v>195828.35139130434</v>
-      </c>
-      <c r="E59" s="16">
-        <v>4600904.7489205301</v>
+        <v>195828.351</v>
+      </c>
+      <c r="E59" s="24">
+        <v>4600905</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -1593,44 +1620,44 @@
         <v>27</v>
       </c>
       <c r="D60" s="15">
-        <v>179315.34079130436</v>
-      </c>
-      <c r="E60" s="16">
-        <v>4212938.4260579497</v>
+        <v>179315.34099999999</v>
+      </c>
+      <c r="E60" s="24">
+        <v>4212938</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="20">
-        <v>2026</v>
-      </c>
-      <c r="B61" s="20">
+      <c r="A61" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B61" s="18">
         <v>2</v>
       </c>
-      <c r="C61" s="20">
+      <c r="C61" s="18">
         <v>28</v>
       </c>
-      <c r="D61" s="21">
-        <v>177297.31779130435</v>
-      </c>
-      <c r="E61" s="22">
-        <v>4165525.8141649901</v>
+      <c r="D61" s="19">
+        <v>177297.318</v>
+      </c>
+      <c r="E61" s="24">
+        <v>4165526</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="26">
-        <v>2026</v>
-      </c>
-      <c r="B62" s="26">
+      <c r="A62" s="22">
+        <v>2026</v>
+      </c>
+      <c r="B62" s="22">
         <v>3</v>
       </c>
-      <c r="C62" s="26">
+      <c r="C62" s="22">
         <v>1</v>
       </c>
-      <c r="D62" s="27">
-        <v>154571.64350313091</v>
-      </c>
-      <c r="E62" s="28">
-        <v>3631596.5393212629</v>
+      <c r="D62" s="23">
+        <v>154571.64350000001</v>
+      </c>
+      <c r="E62" s="24">
+        <v>3631597</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1644,10 +1671,10 @@
         <v>2</v>
       </c>
       <c r="D63" s="7">
-        <v>164267.48195548551</v>
-      </c>
-      <c r="E63" s="10">
-        <v>3859396.235121714</v>
+        <v>164267.48199999999</v>
+      </c>
+      <c r="E63" s="24">
+        <v>3859396</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1661,10 +1688,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="7">
-        <v>190296.90896154233</v>
-      </c>
-      <c r="E64" s="10">
-        <v>4470946.8073571492</v>
+        <v>190296.90900000001</v>
+      </c>
+      <c r="E64" s="24">
+        <v>4470947</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1678,10 +1705,10 @@
         <v>4</v>
       </c>
       <c r="D65" s="7">
-        <v>195099.60506060976</v>
-      </c>
-      <c r="E65" s="10">
-        <v>4583784.1566762151</v>
+        <v>195099.60509999999</v>
+      </c>
+      <c r="E65" s="24">
+        <v>4583784</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1695,10 +1722,10 @@
         <v>5</v>
       </c>
       <c r="D66" s="7">
-        <v>199280.23192232152</v>
-      </c>
-      <c r="E66" s="10">
-        <v>4682006.2477344526</v>
+        <v>199280.23190000001</v>
+      </c>
+      <c r="E66" s="24">
+        <v>4682006</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -1712,10 +1739,10 @@
         <v>6</v>
       </c>
       <c r="D67" s="7">
-        <v>190296.90896154233</v>
-      </c>
-      <c r="E67" s="10">
-        <v>4470946.8073571492</v>
+        <v>190296.90900000001</v>
+      </c>
+      <c r="E67" s="24">
+        <v>4470947</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -1729,10 +1756,10 @@
         <v>7</v>
       </c>
       <c r="D68" s="7">
-        <v>163219.31036491692</v>
-      </c>
-      <c r="E68" s="10">
-        <v>3834769.8791184109</v>
+        <v>163219.31039999999</v>
+      </c>
+      <c r="E68" s="24">
+        <v>3834770</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -1746,10 +1773,10 @@
         <v>8</v>
       </c>
       <c r="D69" s="7">
-        <v>156817.72548292077</v>
-      </c>
-      <c r="E69" s="10">
-        <v>3684367.3021854842</v>
+        <v>156817.7255</v>
+      </c>
+      <c r="E69" s="24">
+        <v>3684367</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -1763,10 +1790,10 @@
         <v>9</v>
       </c>
       <c r="D70" s="7">
-        <v>172294.08453829604</v>
-      </c>
-      <c r="E70" s="10">
-        <v>4047977.9277376132</v>
+        <v>172294.0845</v>
+      </c>
+      <c r="E70" s="24">
+        <v>4047978</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -1780,10 +1807,10 @@
         <v>10</v>
       </c>
       <c r="D71" s="7">
-        <v>170079.15626829298</v>
-      </c>
-      <c r="E71" s="10">
-        <v>3995939.1083404124</v>
+        <v>170079.1563</v>
+      </c>
+      <c r="E71" s="24">
+        <v>3995939</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -1797,10 +1824,10 @@
         <v>11</v>
       </c>
       <c r="D72" s="7">
-        <v>169819.87700619645</v>
-      </c>
-      <c r="E72" s="10">
-        <v>3989847.4498084355</v>
+        <v>169819.87700000001</v>
+      </c>
+      <c r="E72" s="24">
+        <v>3989847</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -1814,10 +1841,10 @@
         <v>12</v>
       </c>
       <c r="D73" s="7">
-        <v>164396.67678052888</v>
-      </c>
-      <c r="E73" s="10">
-        <v>3862431.613855435</v>
+        <v>164396.67679999999</v>
+      </c>
+      <c r="E73" s="24">
+        <v>3862432</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -1831,10 +1858,10 @@
         <v>13</v>
       </c>
       <c r="D74" s="7">
-        <v>158204.55659941444</v>
-      </c>
-      <c r="E74" s="10">
-        <v>3716950.3230367792</v>
+        <v>158204.55660000001</v>
+      </c>
+      <c r="E74" s="24">
+        <v>3716950</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -1848,10 +1875,10 @@
         <v>14</v>
       </c>
       <c r="D75" s="7">
-        <v>143277.67045662727</v>
-      </c>
-      <c r="E75" s="10">
-        <v>3366249.3352589635</v>
+        <v>143277.67050000001</v>
+      </c>
+      <c r="E75" s="24">
+        <v>3366249</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -1865,10 +1892,10 @@
         <v>15</v>
       </c>
       <c r="D76" s="7">
-        <v>140802.55997254423</v>
-      </c>
-      <c r="E76" s="10">
-        <v>3308097.6428481126</v>
+        <v>140802.56</v>
+      </c>
+      <c r="E76" s="24">
+        <v>3308098</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -1882,10 +1909,10 @@
         <v>16</v>
       </c>
       <c r="D77" s="7">
-        <v>160483.15442333318</v>
-      </c>
-      <c r="E77" s="10">
-        <v>3770485.0321484189</v>
+        <v>160483.1544</v>
+      </c>
+      <c r="E77" s="24">
+        <v>3770485</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -1899,10 +1926,10 @@
         <v>17</v>
       </c>
       <c r="D78" s="7">
-        <v>166144.05181694173</v>
-      </c>
-      <c r="E78" s="10">
-        <v>3903485.4642986096</v>
+        <v>166144.05179999999</v>
+      </c>
+      <c r="E78" s="24">
+        <v>3903485</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -1916,10 +1943,10 @@
         <v>18</v>
       </c>
       <c r="D79" s="7">
-        <v>161845.96874830086</v>
-      </c>
-      <c r="E79" s="10">
-        <v>3802503.7884618295</v>
+        <v>161845.9687</v>
+      </c>
+      <c r="E79" s="24">
+        <v>3802504</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -1933,10 +1960,10 @@
         <v>19</v>
       </c>
       <c r="D80" s="7">
-        <v>153712.11014991064</v>
-      </c>
-      <c r="E80" s="10">
-        <v>3611402.1603249446</v>
+        <v>153712.11009999999</v>
+      </c>
+      <c r="E80" s="24">
+        <v>3611402</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -1950,10 +1977,10 @@
         <v>20</v>
       </c>
       <c r="D81" s="7">
-        <v>153660.72659390385</v>
-      </c>
-      <c r="E81" s="10">
-        <v>3610194.9250265216</v>
+        <v>153660.72659999999</v>
+      </c>
+      <c r="E81" s="24">
+        <v>3610195</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -1967,10 +1994,10 @@
         <v>21</v>
       </c>
       <c r="D82" s="7">
-        <v>124137.97659596184</v>
-      </c>
-      <c r="E82" s="10">
-        <v>2916570.1805784795</v>
+        <v>124137.97659999999</v>
+      </c>
+      <c r="E82" s="24">
+        <v>2916570</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -1984,10 +2011,10 @@
         <v>22</v>
       </c>
       <c r="D83" s="7">
-        <v>119182.32394505019</v>
-      </c>
-      <c r="E83" s="10">
-        <v>2800139.1806275449</v>
+        <v>119182.3239</v>
+      </c>
+      <c r="E83" s="24">
+        <v>2800139</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2001,10 +2028,10 @@
         <v>23</v>
       </c>
       <c r="D84" s="7">
-        <v>130520.76865967279</v>
-      </c>
-      <c r="E84" s="10">
-        <v>3066531.2280542441</v>
+        <v>130520.7687</v>
+      </c>
+      <c r="E84" s="24">
+        <v>3066531</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2018,10 +2045,10 @@
         <v>24</v>
       </c>
       <c r="D85" s="7">
-        <v>135563.17480094431</v>
-      </c>
-      <c r="E85" s="10">
-        <v>3185000.4652149593</v>
+        <v>135563.17480000001</v>
+      </c>
+      <c r="E85" s="24">
+        <v>3185000</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -2035,10 +2062,10 @@
         <v>25</v>
       </c>
       <c r="D86" s="7">
-        <v>127154.24603455765</v>
-      </c>
-      <c r="E86" s="10">
-        <v>2987436.1777731278</v>
+        <v>127154.246</v>
+      </c>
+      <c r="E86" s="24">
+        <v>2987436</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2052,10 +2079,10 @@
         <v>26</v>
       </c>
       <c r="D87" s="7">
-        <v>128214.91716029312</v>
-      </c>
-      <c r="E87" s="10">
-        <v>3012356.205161598</v>
+        <v>128214.9172</v>
+      </c>
+      <c r="E87" s="24">
+        <v>3012356</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -2069,10 +2096,10 @@
         <v>27</v>
       </c>
       <c r="D88" s="7">
-        <v>130150.9880887076</v>
-      </c>
-      <c r="E88" s="10">
-        <v>3057843.3871838823</v>
+        <v>130150.9881</v>
+      </c>
+      <c r="E88" s="24">
+        <v>3057843</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -2086,10 +2113,10 @@
         <v>28</v>
       </c>
       <c r="D89" s="7">
-        <v>118012.13759255769</v>
-      </c>
-      <c r="E89" s="10">
-        <v>2772646.1384901837</v>
+        <v>118012.1376</v>
+      </c>
+      <c r="E89" s="24">
+        <v>2772646</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -2103,10 +2130,10 @@
         <v>29</v>
       </c>
       <c r="D90" s="7">
-        <v>115399.7129147677</v>
-      </c>
-      <c r="E90" s="10">
-        <v>2711268.3061524727</v>
+        <v>115399.7129</v>
+      </c>
+      <c r="E90" s="24">
+        <v>2711268</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2120,10 +2147,10 @@
         <v>30</v>
       </c>
       <c r="D91" s="7">
-        <v>124284.22963269848</v>
-      </c>
-      <c r="E91" s="10">
-        <v>2920006.3349082181</v>
+        <v>124284.22960000001</v>
+      </c>
+      <c r="E91" s="24">
+        <v>2920006</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -2137,27 +2164,27 @@
         <v>31</v>
       </c>
       <c r="D92" s="9">
-        <v>128815.11500802798</v>
-      </c>
-      <c r="E92" s="11">
-        <v>3026457.6042108866</v>
+        <v>128815.11500000001</v>
+      </c>
+      <c r="E92" s="24">
+        <v>3026458</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="23">
-        <v>2026</v>
-      </c>
-      <c r="B93" s="23">
+      <c r="A93" s="20">
+        <v>2026</v>
+      </c>
+      <c r="B93" s="20">
         <v>4</v>
       </c>
-      <c r="C93" s="23">
+      <c r="C93" s="20">
         <v>1</v>
       </c>
-      <c r="D93" s="24">
-        <v>135678.90173531568</v>
-      </c>
-      <c r="E93" s="25">
-        <v>3187719.4214532734</v>
+      <c r="D93" s="21">
+        <v>135678.90169999999</v>
+      </c>
+      <c r="E93" s="24">
+        <v>3187719</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -2171,10 +2198,10 @@
         <v>2</v>
       </c>
       <c r="D94" s="7">
-        <v>134504.05417219922</v>
-      </c>
-      <c r="E94" s="10">
-        <v>3160116.8661090434</v>
+        <v>134504.05420000001</v>
+      </c>
+      <c r="E94" s="24">
+        <v>3160117</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -2188,10 +2215,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="7">
-        <v>128459.71513042593</v>
-      </c>
-      <c r="E95" s="10">
-        <v>3018107.6317558894</v>
+        <v>128459.7151</v>
+      </c>
+      <c r="E95" s="24">
+        <v>3018108</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -2205,10 +2232,10 @@
         <v>4</v>
       </c>
       <c r="D96" s="7">
-        <v>101219.22966547139</v>
-      </c>
-      <c r="E96" s="10">
-        <v>2378103.7442255332</v>
+        <v>101219.2297</v>
+      </c>
+      <c r="E96" s="24">
+        <v>2378104</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -2222,10 +2249,10 @@
         <v>5</v>
       </c>
       <c r="D97" s="7">
-        <v>97257.943587270536</v>
-      </c>
-      <c r="E97" s="10">
-        <v>2285034.9737394103</v>
+        <v>97257.943599999999</v>
+      </c>
+      <c r="E97" s="24">
+        <v>2285035</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -2239,10 +2266,10 @@
         <v>6</v>
       </c>
       <c r="D98" s="7">
-        <v>113315.63602285007</v>
-      </c>
-      <c r="E98" s="10">
-        <v>2662303.7855144152</v>
+        <v>113315.636</v>
+      </c>
+      <c r="E98" s="24">
+        <v>2662304</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -2256,10 +2283,10 @@
         <v>7</v>
       </c>
       <c r="D99" s="7">
-        <v>116899.26933336745</v>
-      </c>
-      <c r="E99" s="10">
-        <v>2746499.7611391922</v>
+        <v>116899.2693</v>
+      </c>
+      <c r="E99" s="24">
+        <v>2746500</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -2273,10 +2300,10 @@
         <v>8</v>
       </c>
       <c r="D100" s="7">
-        <v>116691.17527400244</v>
-      </c>
-      <c r="E100" s="10">
-        <v>2741610.6776778526</v>
+        <v>116691.1753</v>
+      </c>
+      <c r="E100" s="24">
+        <v>2741611</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -2290,10 +2317,10 @@
         <v>9</v>
       </c>
       <c r="D101" s="7">
-        <v>116292.53689176546</v>
-      </c>
-      <c r="E101" s="10">
-        <v>2732244.8345221304</v>
+        <v>116292.53690000001</v>
+      </c>
+      <c r="E101" s="24">
+        <v>2732245</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -2307,10 +2334,10 @@
         <v>10</v>
       </c>
       <c r="D102" s="7">
-        <v>101862.72974592153</v>
-      </c>
-      <c r="E102" s="10">
-        <v>2393222.5112403147</v>
+        <v>101862.7297</v>
+      </c>
+      <c r="E102" s="24">
+        <v>2393223</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -2324,10 +2351,10 @@
         <v>11</v>
       </c>
       <c r="D103" s="7">
-        <v>92627.663038175349</v>
-      </c>
-      <c r="E103" s="10">
-        <v>2176248.4561279831</v>
+        <v>92627.663</v>
+      </c>
+      <c r="E103" s="24">
+        <v>2176248</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -2341,10 +2368,10 @@
         <v>12</v>
       </c>
       <c r="D104" s="7">
-        <v>89381.248189381338</v>
-      </c>
-      <c r="E104" s="10">
-        <v>2099975.2881465433</v>
+        <v>89381.248200000002</v>
+      </c>
+      <c r="E104" s="24">
+        <v>2099975</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -2358,10 +2385,10 @@
         <v>13</v>
       </c>
       <c r="D105" s="7">
-        <v>101656.29507457175</v>
-      </c>
-      <c r="E105" s="10">
-        <v>2388372.4144109143</v>
+        <v>101656.2951</v>
+      </c>
+      <c r="E105" s="24">
+        <v>2388372</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -2375,10 +2402,10 @@
         <v>14</v>
       </c>
       <c r="D106" s="7">
-        <v>108240.31815658823</v>
-      </c>
-      <c r="E106" s="10">
-        <v>2543061.301049931</v>
+        <v>108240.31819999999</v>
+      </c>
+      <c r="E106" s="24">
+        <v>2543061</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -2392,10 +2419,10 @@
         <v>15</v>
       </c>
       <c r="D107" s="7">
-        <v>109247.9179510893</v>
-      </c>
-      <c r="E107" s="10">
-        <v>2566734.4395622793</v>
+        <v>109247.91800000001</v>
+      </c>
+      <c r="E107" s="24">
+        <v>2566734</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -2409,10 +2436,10 @@
         <v>16</v>
       </c>
       <c r="D108" s="7">
-        <v>103329.35327644064</v>
-      </c>
-      <c r="E108" s="10">
-        <v>2427680.2217052518</v>
+        <v>103329.3533</v>
+      </c>
+      <c r="E108" s="24">
+        <v>2427680</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -2426,10 +2453,10 @@
         <v>17</v>
       </c>
       <c r="D109" s="7">
-        <v>91322.600432160427</v>
-      </c>
-      <c r="E109" s="10">
-        <v>2145586.552455429</v>
+        <v>91322.600399999996</v>
+      </c>
+      <c r="E109" s="24">
+        <v>2145587</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -2443,10 +2470,10 @@
         <v>18</v>
       </c>
       <c r="D110" s="7">
-        <v>80612.366197197451</v>
-      </c>
-      <c r="E110" s="10">
-        <v>1893954.0492257935</v>
+        <v>80612.366200000004</v>
+      </c>
+      <c r="E110" s="24">
+        <v>1893954</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -2460,10 +2487,10 @@
         <v>19</v>
       </c>
       <c r="D111" s="7">
-        <v>79866.906037006585</v>
-      </c>
-      <c r="E111" s="10">
-        <v>1876439.7725020929</v>
+        <v>79866.906000000003</v>
+      </c>
+      <c r="E111" s="24">
+        <v>1876440</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -2479,8 +2506,8 @@
       <c r="D112" s="7">
         <v>96457.057000000001</v>
       </c>
-      <c r="E112" s="10">
-        <v>2266218.4761412498</v>
+      <c r="E112" s="24">
+        <v>2266218</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -2494,10 +2521,10 @@
         <v>21</v>
       </c>
       <c r="D113" s="7">
-        <v>104147.77765926988</v>
-      </c>
-      <c r="E113" s="10">
-        <v>2446908.7625230802</v>
+        <v>104147.77770000001</v>
+      </c>
+      <c r="E113" s="24">
+        <v>2446909</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -2511,10 +2538,10 @@
         <v>22</v>
       </c>
       <c r="D114" s="7">
-        <v>102279.695613444</v>
-      </c>
-      <c r="E114" s="10">
-        <v>2403018.9510477171</v>
+        <v>102279.69560000001</v>
+      </c>
+      <c r="E114" s="24">
+        <v>2403019</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -2528,10 +2555,10 @@
         <v>23</v>
       </c>
       <c r="D115" s="7">
-        <v>97429.388701657328</v>
-      </c>
-      <c r="E115" s="10">
-        <v>2289063.0054661869</v>
+        <v>97429.388699999996</v>
+      </c>
+      <c r="E115" s="24">
+        <v>2289063</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -2547,8 +2574,8 @@
       <c r="D116" s="7">
         <v>94178.402000000002</v>
       </c>
-      <c r="E116" s="10">
-        <v>2212682.4237013366</v>
+      <c r="E116" s="24">
+        <v>2212682</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -2562,10 +2589,10 @@
         <v>25</v>
       </c>
       <c r="D117" s="7">
-        <v>74356.377690000008</v>
-      </c>
-      <c r="E117" s="10">
-        <v>1746972.1986232176</v>
+        <v>74356.377699999997</v>
+      </c>
+      <c r="E117" s="24">
+        <v>1746972</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -2579,10 +2606,10 @@
         <v>26</v>
       </c>
       <c r="D118" s="7">
-        <v>71440.441310000009</v>
-      </c>
-      <c r="E118" s="10">
-        <v>1678463.4849517187</v>
+        <v>71440.441300000006</v>
+      </c>
+      <c r="E118" s="24">
+        <v>1678463</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -2598,8 +2625,8 @@
       <c r="D119" s="7">
         <v>93693.858999999997</v>
       </c>
-      <c r="E119" s="10">
-        <v>2201298.2872447898</v>
+      <c r="E119" s="24">
+        <v>2201298</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -2613,10 +2640,10 @@
         <v>28</v>
       </c>
       <c r="D120" s="7">
-        <v>96738.638129286104</v>
-      </c>
-      <c r="E120" s="10">
-        <v>2272834.1077763806</v>
+        <v>96738.638099999996</v>
+      </c>
+      <c r="E120" s="24">
+        <v>2272834</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -2630,10 +2657,10 @@
         <v>29</v>
       </c>
       <c r="D121" s="7">
-        <v>95681.813325015028</v>
-      </c>
-      <c r="E121" s="10">
-        <v>2248004.4481125632</v>
+        <v>95681.813299999994</v>
+      </c>
+      <c r="E121" s="24">
+        <v>2248004</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -2647,27 +2674,27 @@
         <v>30</v>
       </c>
       <c r="D122" s="9">
-        <v>90498.199660127633</v>
-      </c>
-      <c r="E122" s="11">
-        <v>2126214.1518484787</v>
+        <v>90498.199699999997</v>
+      </c>
+      <c r="E122" s="24">
+        <v>2126214</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="23">
-        <v>2026</v>
-      </c>
-      <c r="B123" s="23">
+      <c r="A123" s="20">
+        <v>2026</v>
+      </c>
+      <c r="B123" s="20">
         <v>5</v>
       </c>
-      <c r="C123" s="23">
+      <c r="C123" s="20">
         <v>1</v>
       </c>
-      <c r="D123" s="24">
-        <v>82016.81</v>
-      </c>
-      <c r="E123" s="25">
-        <v>1926951</v>
+      <c r="D123" s="21">
+        <v>77522.354999999996</v>
+      </c>
+      <c r="E123" s="24">
+        <v>1821355.52</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -2681,10 +2708,10 @@
         <v>2</v>
       </c>
       <c r="D124" s="7">
-        <v>73027.900000000009</v>
-      </c>
-      <c r="E124" s="10">
-        <v>1715760</v>
+        <v>73027.899999999994</v>
+      </c>
+      <c r="E124" s="24">
+        <v>1715760.1669999999</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -2700,8 +2727,8 @@
       <c r="D125" s="7">
         <v>69030.868000000002</v>
       </c>
-      <c r="E125" s="10">
-        <v>1621852</v>
+      <c r="E125" s="24">
+        <v>1621851.561</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -2715,10 +2742,10 @@
         <v>4</v>
       </c>
       <c r="D126" s="7">
-        <v>75188.5</v>
-      </c>
-      <c r="E126" s="10">
-        <v>1766523</v>
+        <v>77935.490269999995</v>
+      </c>
+      <c r="E126" s="24">
+        <v>1831061.9620000001</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
@@ -2732,10 +2759,10 @@
         <v>5</v>
       </c>
       <c r="D127" s="7">
-        <v>83071.070000000007</v>
-      </c>
-      <c r="E127" s="10">
-        <v>1951720</v>
+        <v>76392.213229999994</v>
+      </c>
+      <c r="E127" s="24">
+        <v>1794803.3089999999</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -2751,8 +2778,8 @@
       <c r="D128" s="7">
         <v>87858.626000000004</v>
       </c>
-      <c r="E128" s="10">
-        <v>2064202</v>
+      <c r="E128" s="24">
+        <v>2064201.912</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -2766,10 +2793,10 @@
         <v>7</v>
       </c>
       <c r="D129" s="7">
-        <v>83725.214999999997</v>
-      </c>
-      <c r="E129" s="10">
-        <v>1967089</v>
+        <v>88219.67</v>
+      </c>
+      <c r="E129" s="24">
+        <v>2072684.4909999999</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -2785,8 +2812,8 @@
       <c r="D130" s="7">
         <v>86682.267000000007</v>
       </c>
-      <c r="E130" s="10">
-        <v>2036564</v>
+      <c r="E130" s="24">
+        <v>2036563.8470000001</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -2802,8 +2829,8 @@
       <c r="D131" s="7">
         <v>70332.619000000006</v>
       </c>
-      <c r="E131" s="10">
-        <v>1652436</v>
+      <c r="E131" s="24">
+        <v>1652435.66</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -2817,10 +2844,10 @@
         <v>10</v>
       </c>
       <c r="D132" s="7">
-        <v>62468.885999999999</v>
-      </c>
-      <c r="E132" s="10">
-        <v>1467681</v>
+        <v>66400.752500000002</v>
+      </c>
+      <c r="E132" s="24">
+        <v>1560058.09</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -2834,10 +2861,10 @@
         <v>11</v>
       </c>
       <c r="D133" s="7">
-        <v>85282.451000000001</v>
-      </c>
-      <c r="E133" s="10">
-        <v>2003676</v>
+        <v>84462.229000000007</v>
+      </c>
+      <c r="E133" s="24">
+        <v>1984404.976</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -2851,10 +2878,10 @@
         <v>12</v>
       </c>
       <c r="D134" s="7">
-        <v>84462.229000000007</v>
-      </c>
-      <c r="E134" s="10">
-        <v>1984405</v>
+        <v>85282.451000000001</v>
+      </c>
+      <c r="E134" s="24">
+        <v>2003675.7509999999</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -2868,10 +2895,10 @@
         <v>13</v>
       </c>
       <c r="D135" s="7">
-        <v>86770.048999999999</v>
-      </c>
-      <c r="E135" s="10">
-        <v>2038626</v>
+        <v>87939.832609999998</v>
+      </c>
+      <c r="E135" s="24">
+        <v>2066109.828</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -2885,10 +2912,10 @@
         <v>14</v>
       </c>
       <c r="D136" s="7">
-        <v>88234.593000000008</v>
-      </c>
-      <c r="E136" s="10">
-        <v>2073035</v>
+        <v>87064.809399999998</v>
+      </c>
+      <c r="E136" s="24">
+        <v>2045551.5209999999</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -2904,8 +2931,8 @@
       <c r="D137" s="7">
         <v>78246.599000000002</v>
       </c>
-      <c r="E137" s="10">
-        <v>1838371</v>
+      <c r="E137" s="24">
+        <v>1838371.3319999999</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -2921,8 +2948,8 @@
       <c r="D138" s="7">
         <v>62496.864999999998</v>
       </c>
-      <c r="E138" s="10">
-        <v>1468338</v>
+      <c r="E138" s="24">
+        <v>1468337.8759999999</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
@@ -2936,10 +2963,10 @@
         <v>17</v>
       </c>
       <c r="D139" s="7">
-        <v>53791.37</v>
-      </c>
-      <c r="E139" s="10">
-        <v>1263806</v>
+        <v>57439.844499999999</v>
+      </c>
+      <c r="E139" s="24">
+        <v>1349525.28</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -2955,8 +2982,8 @@
       <c r="D140" s="7">
         <v>74460.710000000006</v>
       </c>
-      <c r="E140" s="10">
-        <v>1749423</v>
+      <c r="E140" s="24">
+        <v>1749423.443</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
@@ -2972,8 +2999,8 @@
       <c r="D141" s="7">
         <v>77201.607000000004</v>
       </c>
-      <c r="E141" s="10">
-        <v>1813820</v>
+      <c r="E141" s="24">
+        <v>1813819.679</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -2987,10 +3014,10 @@
         <v>20</v>
       </c>
       <c r="D142" s="7">
-        <v>76068.125</v>
-      </c>
-      <c r="E142" s="10">
-        <v>1787189</v>
+        <v>78452.633109999995</v>
+      </c>
+      <c r="E142" s="24">
+        <v>1843212.0179999999</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -3004,10 +3031,10 @@
         <v>21</v>
       </c>
       <c r="D143" s="7">
-        <v>80056.517999999996</v>
-      </c>
-      <c r="E143" s="10">
-        <v>1880895</v>
+        <v>77672.009890000001</v>
+      </c>
+      <c r="E143" s="24">
+        <v>1824871.6</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -3023,8 +3050,8 @@
       <c r="D144" s="7">
         <v>73506.797999999995</v>
       </c>
-      <c r="E144" s="10">
-        <v>1727012</v>
+      <c r="E144" s="24">
+        <v>1727011.6769999999</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
@@ -3040,8 +3067,8 @@
       <c r="D145" s="7">
         <v>60410.472999999998</v>
       </c>
-      <c r="E145" s="10">
-        <v>1419319</v>
+      <c r="E145" s="24">
+        <v>1419318.9620000001</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
@@ -3055,10 +3082,10 @@
         <v>24</v>
       </c>
       <c r="D146" s="7">
-        <v>53038.400999999998</v>
-      </c>
-      <c r="E146" s="10">
-        <v>1246115</v>
+        <v>56686.875500000002</v>
+      </c>
+      <c r="E146" s="24">
+        <v>1331834.5859999999</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
@@ -3074,8 +3101,8 @@
       <c r="D147" s="7">
         <v>74212.452000000005</v>
       </c>
-      <c r="E147" s="10">
-        <v>1743591</v>
+      <c r="E147" s="24">
+        <v>1743590.7239999999</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
@@ -3089,10 +3116,10 @@
         <v>26</v>
       </c>
       <c r="D148" s="7">
-        <v>76526.680000000008</v>
-      </c>
-      <c r="E148" s="10">
-        <v>1797963</v>
+        <v>76526.679999999993</v>
+      </c>
+      <c r="E148" s="24">
+        <v>1797962.55</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
@@ -3108,8 +3135,8 @@
       <c r="D149" s="7">
         <v>77484.763999999996</v>
       </c>
-      <c r="E149" s="10">
-        <v>1820472</v>
+      <c r="E149" s="24">
+        <v>1820472.335</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
@@ -3125,8 +3152,8 @@
       <c r="D150" s="7">
         <v>76059.827000000005</v>
       </c>
-      <c r="E150" s="10">
-        <v>1786994</v>
+      <c r="E150" s="24">
+        <v>1786994.0319999999</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
@@ -3142,8 +3169,8 @@
       <c r="D151" s="7">
         <v>73851.479000000007</v>
       </c>
-      <c r="E151" s="10">
-        <v>1735110</v>
+      <c r="E151" s="24">
+        <v>1735109.814</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
@@ -3159,8 +3186,8 @@
       <c r="D152" s="7">
         <v>58205.732000000004</v>
       </c>
-      <c r="E152" s="10">
-        <v>1367519</v>
+      <c r="E152" s="24">
+        <v>1367520</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
@@ -3174,10 +3201,10 @@
         <v>31</v>
       </c>
       <c r="D153" s="7">
-        <v>59582.381000000001</v>
-      </c>
-      <c r="E153" s="10">
-        <v>1399863</v>
+        <v>52285.432000000001</v>
+      </c>
+      <c r="E153" s="25">
+        <v>1228425</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
@@ -3191,10 +3218,10 @@
         <v>1</v>
       </c>
       <c r="D154" s="7">
-        <v>68993.345000000001</v>
-      </c>
-      <c r="E154" s="10">
-        <v>1620970</v>
+        <v>71087.096359999618</v>
+      </c>
+      <c r="E154" s="24">
+        <v>1670161.7921668964</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
@@ -3208,10 +3235,10 @@
         <v>2</v>
       </c>
       <c r="D155" s="7">
-        <v>69791.712</v>
-      </c>
-      <c r="E155" s="10">
-        <v>1639727</v>
+        <v>74546.767000000007</v>
+      </c>
+      <c r="E155" s="24">
+        <v>1751445.3163545805</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
@@ -3225,10 +3252,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="7">
-        <v>74546.767000000007</v>
-      </c>
-      <c r="E156" s="10">
-        <v>1751445</v>
+        <v>67697.960640000005</v>
+      </c>
+      <c r="E156" s="24">
+        <v>1590535.4566172499</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
@@ -3244,8 +3271,8 @@
       <c r="D157" s="7">
         <v>76226.192999999999</v>
       </c>
-      <c r="E157" s="10">
-        <v>1790903</v>
+      <c r="E157" s="24">
+        <v>1790902.732420177</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
@@ -3261,8 +3288,8 @@
       <c r="D158" s="7">
         <v>72421.864000000001</v>
       </c>
-      <c r="E158" s="10">
-        <v>1701522</v>
+      <c r="E158" s="24">
+        <v>1701521.6032704462</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
@@ -3276,10 +3303,10 @@
         <v>6</v>
       </c>
       <c r="D159" s="7">
-        <v>57067.635999999999</v>
-      </c>
-      <c r="E159" s="10">
-        <v>1340780</v>
+        <v>55489.094969999998</v>
+      </c>
+      <c r="E159" s="24">
+        <v>1303693.2305053682</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
@@ -3293,10 +3320,10 @@
         <v>7</v>
       </c>
       <c r="D160" s="7">
-        <v>51734.510999999999</v>
-      </c>
-      <c r="E160" s="10">
-        <v>1215481</v>
+        <v>53313.052029999999</v>
+      </c>
+      <c r="E160" s="24">
+        <v>1252568.0057796675</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
@@ -3312,8 +3339,8 @@
       <c r="D161" s="7">
         <v>70525.248999999996</v>
       </c>
-      <c r="E161" s="10">
-        <v>1656961</v>
+      <c r="E161" s="24">
+        <v>1656961.4218922537</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
@@ -3329,8 +3356,8 @@
       <c r="D162" s="7">
         <v>73481.587</v>
       </c>
-      <c r="E162" s="10">
-        <v>1726419</v>
+      <c r="E162" s="24">
+        <v>1726419.3548387096</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
@@ -3346,8 +3373,8 @@
       <c r="D163" s="7">
         <v>73664.275000000009</v>
       </c>
-      <c r="E163" s="10">
-        <v>1730712</v>
+      <c r="E163" s="24">
+        <v>1730711.5334915305</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
@@ -3363,8 +3390,8 @@
       <c r="D164" s="7">
         <v>73392.505000000005</v>
       </c>
-      <c r="E164" s="10">
-        <v>1724326</v>
+      <c r="E164" s="24">
+        <v>1724326.4102624345</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
@@ -3380,8 +3407,8 @@
       <c r="D165" s="7">
         <v>70757.150999999998</v>
       </c>
-      <c r="E165" s="10">
-        <v>1662410</v>
+      <c r="E165" s="24">
+        <v>1662409.8630265724</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
@@ -3395,10 +3422,10 @@
         <v>13</v>
       </c>
       <c r="D166" s="7">
-        <v>57319.880000000005</v>
-      </c>
-      <c r="E166" s="10">
-        <v>1346707</v>
+        <v>55043.31162</v>
+      </c>
+      <c r="E166" s="24">
+        <v>1293219.7359208702</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
@@ -3412,10 +3439,10 @@
         <v>14</v>
       </c>
       <c r="D167" s="7">
-        <v>50608.182000000001</v>
-      </c>
-      <c r="E167" s="10">
-        <v>1189018</v>
+        <v>52884.750380000005</v>
+      </c>
+      <c r="E167" s="24">
+        <v>1242505.2364729929</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
@@ -3431,8 +3458,8 @@
       <c r="D168" s="7">
         <v>69444.928</v>
       </c>
-      <c r="E168" s="10">
-        <v>1631580</v>
+      <c r="E168" s="24">
+        <v>1631579.7288724948</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
@@ -3448,8 +3475,8 @@
       <c r="D169" s="7">
         <v>72265.292000000001</v>
       </c>
-      <c r="E169" s="10">
-        <v>1697843</v>
+      <c r="E169" s="24">
+        <v>1697843.0091863824</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
@@ -3465,8 +3492,8 @@
       <c r="D170" s="7">
         <v>72273.718999999997</v>
       </c>
-      <c r="E170" s="10">
-        <v>1698041</v>
+      <c r="E170" s="24">
+        <v>1698040.9980499493</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
@@ -3482,8 +3509,8 @@
       <c r="D171" s="7">
         <v>72500.576000000001</v>
       </c>
-      <c r="E171" s="10">
-        <v>1703371</v>
+      <c r="E171" s="24">
+        <v>1703370.9090054743</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
@@ -3499,8 +3526,8 @@
       <c r="D172" s="7">
         <v>71414.945000000007</v>
       </c>
-      <c r="E172" s="10">
-        <v>1677864</v>
+      <c r="E172" s="24">
+        <v>1677864.4597420297</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
@@ -3514,10 +3541,10 @@
         <v>20</v>
       </c>
       <c r="D173" s="7">
-        <v>55325.203000000001</v>
-      </c>
-      <c r="E173" s="10">
-        <v>1299843</v>
+        <v>52962.815070000004</v>
+      </c>
+      <c r="E173" s="24">
+        <v>1244339.3339285294</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
@@ -3531,10 +3558,10 @@
         <v>21</v>
       </c>
       <c r="D174" s="7">
-        <v>48523.453999999998</v>
-      </c>
-      <c r="E174" s="10">
-        <v>1140038</v>
+        <v>50885.841930000002</v>
+      </c>
+      <c r="E174" s="24">
+        <v>1195541.7129901557</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
@@ -3550,8 +3577,8 @@
       <c r="D175" s="7">
         <v>67868.956000000006</v>
       </c>
-      <c r="E175" s="10">
-        <v>1594553</v>
+      <c r="E175" s="24">
+        <v>1594552.9215515824</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
@@ -3567,8 +3594,8 @@
       <c r="D176" s="7">
         <v>71139.453999999998</v>
       </c>
-      <c r="E176" s="10">
-        <v>1671392</v>
+      <c r="E176" s="24">
+        <v>1671391.9131640154</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
@@ -3584,8 +3611,8 @@
       <c r="D177" s="7">
         <v>71671.005000000005</v>
       </c>
-      <c r="E177" s="10">
-        <v>1683880</v>
+      <c r="E177" s="24">
+        <v>1683880.4830486572</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
@@ -3601,8 +3628,8 @@
       <c r="D178" s="7">
         <v>71825.288</v>
       </c>
-      <c r="E178" s="10">
-        <v>1687505</v>
+      <c r="E178" s="24">
+        <v>1687505.2980288041</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
@@ -3618,8 +3645,8 @@
       <c r="D179" s="7">
         <v>69482.726999999999</v>
       </c>
-      <c r="E179" s="10">
-        <v>1632468</v>
+      <c r="E179" s="24">
+        <v>1632467.8006719451</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
@@ -3633,10 +3660,10 @@
         <v>27</v>
       </c>
       <c r="D180" s="7">
-        <v>55313.917000000001</v>
-      </c>
-      <c r="E180" s="10">
-        <v>1299577</v>
+        <v>52443.986970000005</v>
+      </c>
+      <c r="E180" s="24">
+        <v>1232149.683293001</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
@@ -3650,10 +3677,10 @@
         <v>28</v>
       </c>
       <c r="D181" s="7">
-        <v>47517.43</v>
-      </c>
-      <c r="E181" s="10">
-        <v>1116402</v>
+        <v>50387.360030000003</v>
+      </c>
+      <c r="E181" s="24">
+        <v>1183830.0878697459</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
@@ -3669,8 +3696,8 @@
       <c r="D182" s="7">
         <v>68691.902000000002</v>
       </c>
-      <c r="E182" s="10">
-        <v>1613888</v>
+      <c r="E182" s="24">
+        <v>1613887.6958860983</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
@@ -3686,8 +3713,8 @@
       <c r="D183" s="7">
         <v>71840.22</v>
       </c>
-      <c r="E183" s="10">
-        <v>1687856</v>
+      <c r="E183" s="24">
+        <v>1687854.11916453</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
@@ -3701,10 +3728,10 @@
         <v>1</v>
       </c>
       <c r="D184" s="7">
-        <v>68254.111000000004</v>
-      </c>
-      <c r="E184" s="10">
-        <v>1603602</v>
+        <v>68759.206408532787</v>
+      </c>
+      <c r="E184" s="26">
+        <v>1615468.9849994779</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
@@ -3718,10 +3745,10 @@
         <v>2</v>
       </c>
       <c r="D185" s="7">
-        <v>68492.510999999999</v>
-      </c>
-      <c r="E185" s="10">
-        <v>1609203</v>
+        <v>68818.416408532779</v>
+      </c>
+      <c r="E185" s="26">
+        <v>1616860.0993476207</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
@@ -3735,10 +3762,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="7">
-        <v>66198.959000000003</v>
-      </c>
-      <c r="E186" s="10">
-        <v>1555317</v>
+        <v>67741.843988532783</v>
+      </c>
+      <c r="E186" s="26">
+        <v>1591566.4776574203</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
@@ -3752,10 +3779,10 @@
         <v>4</v>
       </c>
       <c r="D187" s="7">
-        <v>51486.328000000001</v>
-      </c>
-      <c r="E187" s="10">
-        <v>1209650</v>
+        <v>52528.380408532779</v>
+      </c>
+      <c r="E187" s="26">
+        <v>1234132.4720657091</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
@@ -3769,10 +3796,10 @@
         <v>5</v>
       </c>
       <c r="D188" s="7">
-        <v>45039.393000000004</v>
-      </c>
-      <c r="E188" s="10">
-        <v>1058182</v>
+        <v>46067.395408532779</v>
+      </c>
+      <c r="E188" s="26">
+        <v>1082334.3140411337</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
@@ -3786,10 +3813,10 @@
         <v>6</v>
       </c>
       <c r="D189" s="7">
-        <v>64709.966</v>
-      </c>
-      <c r="E189" s="10">
-        <v>1520334</v>
+        <v>65902.035408532785</v>
+      </c>
+      <c r="E189" s="26">
+        <v>1548340.9395139625</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
@@ -3803,10 +3830,10 @@
         <v>7</v>
       </c>
       <c r="D190" s="7">
-        <v>68368.540999999997</v>
-      </c>
-      <c r="E190" s="10">
-        <v>1606290</v>
+        <v>68694.446408532778</v>
+      </c>
+      <c r="E190" s="26">
+        <v>1613947.4757073696</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
@@ -3820,10 +3847,10 @@
         <v>8</v>
       </c>
       <c r="D191" s="7">
-        <v>67424.55</v>
-      </c>
-      <c r="E191" s="10">
-        <v>1584112</v>
+        <v>68580.016408532785</v>
+      </c>
+      <c r="E191" s="26">
+        <v>1611258.9904032324</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
@@ -3837,10 +3864,10 @@
         <v>9</v>
       </c>
       <c r="D192" s="7">
-        <v>67981.835000000006</v>
-      </c>
-      <c r="E192" s="10">
-        <v>1597205</v>
+        <v>68307.740408532787</v>
+      </c>
+      <c r="E192" s="26">
+        <v>1604861.9789143805</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
@@ -3854,10 +3881,10 @@
         <v>10</v>
       </c>
       <c r="D193" s="7">
-        <v>66312.309000000008</v>
-      </c>
-      <c r="E193" s="10">
-        <v>1557980</v>
+        <v>66638.214408532789</v>
+      </c>
+      <c r="E193" s="26">
+        <v>1565637.1592353166</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
@@ -3871,10 +3898,10 @@
         <v>11</v>
       </c>
       <c r="D194" s="7">
-        <v>52202.474999999999</v>
-      </c>
-      <c r="E194" s="10">
-        <v>1226475</v>
+        <v>52357.45640853278</v>
+      </c>
+      <c r="E194" s="26">
+        <v>1230116.6837049264</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
@@ -3888,10 +3915,10 @@
         <v>12</v>
       </c>
       <c r="D195" s="7">
-        <v>45456.139000000003</v>
-      </c>
-      <c r="E195" s="10">
-        <v>1067973</v>
+        <v>45782.044408532784</v>
+      </c>
+      <c r="E195" s="26">
+        <v>1075630.1108599671</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
@@ -3905,10 +3932,10 @@
         <v>13</v>
       </c>
       <c r="D196" s="7">
-        <v>63672.012999999999</v>
-      </c>
-      <c r="E196" s="10">
-        <v>1495947</v>
+        <v>65035.871408532781</v>
+      </c>
+      <c r="E196" s="26">
+        <v>1527990.7762265999</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
@@ -3922,10 +3949,10 @@
         <v>14</v>
       </c>
       <c r="D197" s="7">
-        <v>67855.536000000007</v>
-      </c>
-      <c r="E197" s="10">
-        <v>1594238</v>
+        <v>68181.441408532788</v>
+      </c>
+      <c r="E197" s="26">
+        <v>1601894.6363868334</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
@@ -3939,10 +3966,10 @@
         <v>15</v>
       </c>
       <c r="D198" s="7">
-        <v>68433.301000000007</v>
-      </c>
-      <c r="E198" s="10">
-        <v>1607812</v>
+        <v>67750.455408532784</v>
+      </c>
+      <c r="E198" s="26">
+        <v>1591768.7993922604</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
@@ -3956,10 +3983,10 @@
         <v>16</v>
       </c>
       <c r="D199" s="7">
-        <v>67885.510999999999</v>
-      </c>
-      <c r="E199" s="10">
-        <v>1594942</v>
+        <v>68211.416408532779</v>
+      </c>
+      <c r="E199" s="26">
+        <v>1602598.8865571688</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
@@ -3973,10 +4000,10 @@
         <v>17</v>
       </c>
       <c r="D200" s="7">
-        <v>65804.812000000005</v>
-      </c>
-      <c r="E200" s="10">
-        <v>1546057</v>
+        <v>56027.649744016657</v>
+      </c>
+      <c r="E200" s="26">
+        <v>1316346.3511504512</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
@@ -3990,10 +4017,10 @@
         <v>18</v>
       </c>
       <c r="D201" s="7">
-        <v>52031.550999999999</v>
-      </c>
-      <c r="E201" s="10">
-        <v>1222460</v>
+        <v>51812.233408532782</v>
+      </c>
+      <c r="E201" s="26">
+        <v>1217306.8958610243</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
@@ -4007,10 +4034,10 @@
         <v>19</v>
       </c>
       <c r="D202" s="7">
-        <v>45741.49</v>
-      </c>
-      <c r="E202" s="10">
-        <v>1074677</v>
+        <v>45365.298408532784</v>
+      </c>
+      <c r="E202" s="26">
+        <v>1065838.8367486498</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
@@ -4024,10 +4051,10 @@
         <v>20</v>
       </c>
       <c r="D203" s="7">
-        <v>65576.13</v>
-      </c>
-      <c r="E203" s="10">
-        <v>1540684</v>
+        <v>63997.91840853278</v>
+      </c>
+      <c r="E203" s="26">
+        <v>1503604.5017628639</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
@@ -4041,10 +4068,10 @@
         <v>21</v>
       </c>
       <c r="D204" s="7">
-        <v>67436.009000000005</v>
-      </c>
-      <c r="E204" s="10">
-        <v>1584381</v>
+        <v>64977.852768532779</v>
+      </c>
+      <c r="E204" s="26">
+        <v>1526627.6523866451</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
@@ -4058,10 +4085,10 @@
         <v>22</v>
       </c>
       <c r="D205" s="7">
-        <v>64830.317000000003</v>
-      </c>
-      <c r="E205" s="10">
-        <v>1523161</v>
+        <v>65630.902741866114</v>
+      </c>
+      <c r="E205" s="26">
+        <v>1541970.7901667203</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
@@ -4075,10 +4102,10 @@
         <v>23</v>
       </c>
       <c r="D206" s="7">
-        <v>63648.666000000005</v>
-      </c>
-      <c r="E206" s="10">
-        <v>1495399</v>
+        <v>66283.952715199455</v>
+      </c>
+      <c r="E206" s="26">
+        <v>1557313.9279467952</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
@@ -4092,10 +4119,10 @@
         <v>24</v>
       </c>
       <c r="D207" s="7">
-        <v>60848.978999999999</v>
-      </c>
-      <c r="E207" s="10">
-        <v>1429621</v>
+        <v>65117.17040853278</v>
+      </c>
+      <c r="E207" s="26">
+        <v>1529900.8624517252</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
@@ -4109,10 +4136,10 @@
         <v>25</v>
       </c>
       <c r="D208" s="7">
-        <v>49069.451999999997</v>
-      </c>
-      <c r="E208" s="10">
-        <v>1152866</v>
+        <v>49395.357408532778</v>
+      </c>
+      <c r="E208" s="26">
+        <v>1160523.3984571758</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
@@ -4126,10 +4153,10 @@
         <v>26</v>
       </c>
       <c r="D209" s="7">
-        <v>40990.391000000003</v>
-      </c>
-      <c r="E209" s="10">
-        <v>963052</v>
+        <v>41316.296408532784</v>
+      </c>
+      <c r="E209" s="26">
+        <v>970709.21712597285</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
@@ -4143,10 +4170,10 @@
         <v>27</v>
       </c>
       <c r="D210" s="7">
-        <v>59778.144</v>
-      </c>
-      <c r="E210" s="10">
-        <v>1404463</v>
+        <v>60104.049408532781</v>
+      </c>
+      <c r="E210" s="26">
+        <v>1412119.6675171575</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
@@ -4160,10 +4187,10 @@
         <v>28</v>
       </c>
       <c r="D211" s="7">
-        <v>65577.732000000004</v>
-      </c>
-      <c r="E211" s="10">
-        <v>1540722</v>
+        <v>58147.408818532778</v>
+      </c>
+      <c r="E211" s="26">
+        <v>1366149.2098426516</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
@@ -4177,10 +4204,10 @@
         <v>29</v>
       </c>
       <c r="D212" s="7">
-        <v>55484.22</v>
-      </c>
-      <c r="E212" s="10">
-        <v>1303579</v>
+        <v>59315.519998532785</v>
+      </c>
+      <c r="E212" s="26">
+        <v>1393593.496664539</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
@@ -4194,10 +4221,10 @@
         <v>30</v>
       </c>
       <c r="D213" s="7">
-        <v>54154.724999999999</v>
-      </c>
-      <c r="E213" s="10">
-        <v>1272343</v>
+        <v>58731.464408532782</v>
+      </c>
+      <c r="E213" s="26">
+        <v>1379871.3532535953</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
@@ -4211,10 +4238,10 @@
         <v>31</v>
       </c>
       <c r="D214" s="7">
-        <v>64791.264999999999</v>
-      </c>
-      <c r="E214" s="10">
-        <v>1522244</v>
+        <v>59957.904828532781</v>
+      </c>
+      <c r="E214" s="27">
+        <v>1408686.061333383</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
@@ -4230,8 +4257,8 @@
       <c r="D215" s="7">
         <v>45184.762999999999</v>
       </c>
-      <c r="E215" s="10">
-        <v>1061597</v>
+      <c r="E215" s="26">
+        <v>1061597.2323379461</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
@@ -4247,8 +4274,8 @@
       <c r="D216" s="7">
         <v>41144.476999999999</v>
       </c>
-      <c r="E216" s="10">
-        <v>966672</v>
+      <c r="E216" s="26">
+        <v>966672.39151375601</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
@@ -4262,10 +4289,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="7">
-        <v>57923.317000000003</v>
-      </c>
-      <c r="E217" s="10">
-        <v>1360884</v>
+        <v>56602.517</v>
+      </c>
+      <c r="E217" s="26">
+        <v>1329852.6184714423</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
@@ -4279,10 +4306,10 @@
         <v>4</v>
       </c>
       <c r="D218" s="7">
-        <v>56602.517</v>
-      </c>
-      <c r="E218" s="10">
-        <v>1329853</v>
+        <v>57923.317000000003</v>
+      </c>
+      <c r="E218" s="26">
+        <v>1360884.2656767615</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
@@ -4298,8 +4325,8 @@
       <c r="D219" s="7">
         <v>59824.775000000001</v>
       </c>
-      <c r="E219" s="10">
-        <v>1405558</v>
+      <c r="E219" s="26">
+        <v>1405558.2313276788</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
@@ -4315,8 +4342,8 @@
       <c r="D220" s="7">
         <v>60421.622000000003</v>
       </c>
-      <c r="E220" s="10">
-        <v>1419581</v>
+      <c r="E220" s="26">
+        <v>1419580.9036017198</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
@@ -4332,8 +4359,8 @@
       <c r="D221" s="7">
         <v>55519.575000000004</v>
       </c>
-      <c r="E221" s="10">
-        <v>1304409</v>
+      <c r="E221" s="26">
+        <v>1304409.3461457135</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
@@ -4347,10 +4374,10 @@
         <v>8</v>
       </c>
       <c r="D222" s="7">
-        <v>50748.008000000002</v>
-      </c>
-      <c r="E222" s="10">
-        <v>1192303</v>
+        <v>49225.567759999998</v>
+      </c>
+      <c r="E222" s="26">
+        <v>1156534.2612127904</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
@@ -4364,10 +4391,10 @@
         <v>9</v>
       </c>
       <c r="D223" s="7">
-        <v>44153.949000000001</v>
-      </c>
-      <c r="E223" s="10">
-        <v>1037379</v>
+        <v>44019.303</v>
+      </c>
+      <c r="E223" s="26">
+        <v>1034215.2338885887</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
@@ -4383,8 +4410,8 @@
       <c r="D224" s="7">
         <v>60906.387999999999</v>
       </c>
-      <c r="E224" s="10">
-        <v>1430970</v>
+      <c r="E224" s="26">
+        <v>1430970.2793506098</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
@@ -4398,10 +4425,10 @@
         <v>11</v>
       </c>
       <c r="D225" s="7">
-        <v>67140.217000000004</v>
-      </c>
-      <c r="E225" s="10">
-        <v>1577432</v>
+        <v>65970.903999999995</v>
+      </c>
+      <c r="E225" s="26">
+        <v>1549958.9784554658</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
@@ -4417,8 +4444,8 @@
       <c r="D226" s="7">
         <v>68276.835999999996</v>
       </c>
-      <c r="E226" s="10">
-        <v>1604136</v>
+      <c r="E226" s="26">
+        <v>1604135.8926767376</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
@@ -4434,8 +4461,8 @@
       <c r="D227" s="7">
         <v>65970.903999999995</v>
       </c>
-      <c r="E227" s="10">
-        <v>1549959</v>
+      <c r="E227" s="26">
+        <v>1549958.9784554658</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
@@ -4451,8 +4478,8 @@
       <c r="D228" s="7">
         <v>64670.900999999998</v>
       </c>
-      <c r="E228" s="10">
-        <v>1519416</v>
+      <c r="E228" s="26">
+        <v>1519415.9481239573</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
@@ -4466,10 +4493,10 @@
         <v>15</v>
       </c>
       <c r="D229" s="7">
-        <v>51074.519</v>
-      </c>
-      <c r="E229" s="10">
-        <v>1199975</v>
+        <v>49835.611000000004</v>
+      </c>
+      <c r="E229" s="26">
+        <v>1170866.9736625708</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
@@ -4485,8 +4512,8 @@
       <c r="D230" s="7">
         <v>44836.987000000001</v>
       </c>
-      <c r="E230" s="10">
-        <v>1053426</v>
+      <c r="E230" s="26">
+        <v>1053426.3797194746</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
@@ -4502,8 +4529,8 @@
       <c r="D231" s="7">
         <v>46736.928</v>
       </c>
-      <c r="E231" s="10">
-        <v>1098065</v>
+      <c r="E231" s="26">
+        <v>1098064.7040857081</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
@@ -4517,10 +4544,10 @@
         <v>18</v>
       </c>
       <c r="D232" s="7">
-        <v>69387.221000000005</v>
-      </c>
-      <c r="E232" s="10">
-        <v>1630224</v>
+        <v>67140.217000000004</v>
+      </c>
+      <c r="E232" s="26">
+        <v>1577431.5015388953</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
@@ -4536,8 +4563,8 @@
       <c r="D233" s="7">
         <v>68502.881999999998</v>
       </c>
-      <c r="E233" s="10">
-        <v>1609447</v>
+      <c r="E233" s="26">
+        <v>1609446.7495242346</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
@@ -4553,8 +4580,8 @@
       <c r="D234" s="7">
         <v>69371.534</v>
       </c>
-      <c r="E234" s="10">
-        <v>1629855</v>
+      <c r="E234" s="26">
+        <v>1629855.3673378285</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
@@ -4570,8 +4597,8 @@
       <c r="D235" s="7">
         <v>66145.873999999996</v>
       </c>
-      <c r="E235" s="10">
-        <v>1554070</v>
+      <c r="E235" s="26">
+        <v>1554069.8259051286</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
@@ -4585,10 +4612,10 @@
         <v>22</v>
       </c>
       <c r="D236" s="7">
-        <v>52131.326999999997</v>
-      </c>
-      <c r="E236" s="10">
-        <v>1224804</v>
+        <v>50567.387189999994</v>
+      </c>
+      <c r="E236" s="26">
+        <v>1188059.7511923499</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
@@ -4602,10 +4629,10 @@
         <v>23</v>
       </c>
       <c r="D237" s="7">
-        <v>44240.336000000003</v>
-      </c>
-      <c r="E237" s="10">
-        <v>1039408</v>
+        <v>45676.389240000004</v>
+      </c>
+      <c r="E237" s="26">
+        <v>1073147.7865751944</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
@@ -4619,10 +4646,10 @@
         <v>24</v>
       </c>
       <c r="D238" s="7">
-        <v>65168.813999999998</v>
-      </c>
-      <c r="E238" s="10">
-        <v>1531114</v>
+        <v>62471.483</v>
+      </c>
+      <c r="E238" s="26">
+        <v>1467741.5360759343</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
@@ -4636,10 +4663,10 @@
         <v>25</v>
       </c>
       <c r="D239" s="7">
-        <v>67795.885999999999</v>
-      </c>
-      <c r="E239" s="10">
-        <v>1592836</v>
+        <v>68934.65833333334</v>
+      </c>
+      <c r="E239" s="26">
+        <v>1619591.1550720893</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
@@ -4653,10 +4680,10 @@
         <v>26</v>
       </c>
       <c r="D240" s="7">
-        <v>68581.637000000002</v>
-      </c>
-      <c r="E240" s="10">
-        <v>1611297</v>
+        <v>69720.409333333344</v>
+      </c>
+      <c r="E240" s="26">
+        <v>1638052.048336192</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
@@ -4670,10 +4697,10 @@
         <v>27</v>
       </c>
       <c r="D241" s="7">
-        <v>68740.038</v>
-      </c>
-      <c r="E241" s="10">
-        <v>1615019</v>
+        <v>69878.810333333342</v>
+      </c>
+      <c r="E241" s="26">
+        <v>1641773.6140153029</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
@@ -4689,8 +4716,8 @@
       <c r="D242" s="7">
         <v>67650.433000000005</v>
       </c>
-      <c r="E242" s="10">
-        <v>1589419</v>
+      <c r="E242" s="26">
+        <v>1589418.8144632662</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
@@ -4704,10 +4731,10 @@
         <v>29</v>
       </c>
       <c r="D243" s="7">
-        <v>49835.611000000004</v>
-      </c>
-      <c r="E243" s="10">
-        <v>1170867</v>
+        <v>51074.519</v>
+      </c>
+      <c r="E243" s="26">
+        <v>1199974.6023541573</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
@@ -4721,10 +4748,10 @@
         <v>30</v>
       </c>
       <c r="D244" s="7">
-        <v>44019.303</v>
-      </c>
-      <c r="E244" s="10">
-        <v>1034215</v>
+        <v>45804.275810000006</v>
+      </c>
+      <c r="E244" s="26">
+        <v>1076152.4284002539</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
@@ -4738,10 +4765,10 @@
         <v>31</v>
       </c>
       <c r="D245" s="7">
-        <v>62471.483</v>
-      </c>
-      <c r="E245" s="10">
-        <v>1467742</v>
+        <v>65168.813999999998</v>
+      </c>
+      <c r="E245" s="27">
+        <v>1531114.207175246</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
@@ -4755,10 +4782,10 @@
         <v>1</v>
       </c>
       <c r="D246" s="7">
-        <v>66958.892999999996</v>
-      </c>
-      <c r="E246" s="10">
-        <v>1573171</v>
+        <v>67439.561725658816</v>
+      </c>
+      <c r="E246" s="26">
+        <v>1584464.4814899988</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
@@ -4772,10 +4799,10 @@
         <v>2</v>
       </c>
       <c r="D247" s="7">
-        <v>67219.368000000002</v>
-      </c>
-      <c r="E247" s="10">
-        <v>1579291</v>
+        <v>67542.154725658824</v>
+      </c>
+      <c r="E247" s="26">
+        <v>1586874.8613974301</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
@@ -4789,10 +4816,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="7">
-        <v>67018.346000000005</v>
-      </c>
-      <c r="E248" s="10">
-        <v>1574568</v>
+        <v>65555.381725658837</v>
+      </c>
+      <c r="E248" s="26">
+        <v>1540196.4552700429</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
@@ -4806,10 +4833,10 @@
         <v>4</v>
       </c>
       <c r="D249" s="7">
-        <v>64816.08</v>
-      </c>
-      <c r="E249" s="10">
-        <v>1522827</v>
+        <v>64737.314725658827</v>
+      </c>
+      <c r="E249" s="26">
+        <v>1520976.3110132937</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
@@ -4823,10 +4850,10 @@
         <v>5</v>
       </c>
       <c r="D250" s="7">
-        <v>50237.768000000004</v>
-      </c>
-      <c r="E250" s="10">
-        <v>1180315</v>
+        <v>49341.676174958833</v>
+      </c>
+      <c r="E250" s="26">
+        <v>1159262.1801790013</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
@@ -4840,10 +4867,10 @@
         <v>6</v>
       </c>
       <c r="D251" s="7">
-        <v>42285.313000000002</v>
-      </c>
-      <c r="E251" s="10">
-        <v>993476</v>
+        <v>45612.996010658833</v>
+      </c>
+      <c r="E251" s="26">
+        <v>1071658.3889918199</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
@@ -4857,10 +4884,10 @@
         <v>7</v>
       </c>
       <c r="D252" s="7">
-        <v>63023.54</v>
-      </c>
-      <c r="E252" s="10">
-        <v>1480712</v>
+        <v>63703.502725658829</v>
+      </c>
+      <c r="E252" s="26">
+        <v>1496687.327623965</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
@@ -4874,10 +4901,10 @@
         <v>8</v>
       </c>
       <c r="D253" s="7">
-        <v>66700.259999999995</v>
-      </c>
-      <c r="E253" s="10">
-        <v>1567095</v>
+        <v>67698.194725658817</v>
+      </c>
+      <c r="E253" s="26">
+        <v>1590540.9563625406</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
@@ -4891,10 +4918,10 @@
         <v>9</v>
       </c>
       <c r="D254" s="7">
-        <v>66925.05</v>
-      </c>
-      <c r="E254" s="10">
-        <v>1572376</v>
+        <v>67958.669725658823</v>
+      </c>
+      <c r="E254" s="26">
+        <v>1596660.7082597283</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
@@ -4908,10 +4935,10 @@
         <v>10</v>
       </c>
       <c r="D255" s="7">
-        <v>67620.400999999998</v>
-      </c>
-      <c r="E255" s="10">
-        <v>1588713</v>
+        <v>67757.647725658826</v>
+      </c>
+      <c r="E255" s="26">
+        <v>1591937.7798947166</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
@@ -4925,10 +4952,10 @@
         <v>11</v>
       </c>
       <c r="D256" s="7">
-        <v>64093.084000000003</v>
-      </c>
-      <c r="E256" s="10">
-        <v>1505840</v>
+        <v>64832.385725658831</v>
+      </c>
+      <c r="E256" s="26">
+        <v>1523209.9646561292</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
@@ -4942,10 +4969,10 @@
         <v>12</v>
       </c>
       <c r="D257" s="7">
-        <v>49233.478999999999</v>
-      </c>
-      <c r="E257" s="10">
-        <v>1156720</v>
+        <v>48388.688440658829</v>
+      </c>
+      <c r="E257" s="26">
+        <v>1136872.1293296719</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
@@ -4959,10 +4986,10 @@
         <v>13</v>
       </c>
       <c r="D258" s="7">
-        <v>43938.118999999999</v>
-      </c>
-      <c r="E258" s="10">
-        <v>1032308</v>
+        <v>46510.469896358831</v>
+      </c>
+      <c r="E258" s="26">
+        <v>1092744.1650343919</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
@@ -4976,10 +5003,10 @@
         <v>14</v>
       </c>
       <c r="D259" s="7">
-        <v>62964.201000000001</v>
-      </c>
-      <c r="E259" s="10">
-        <v>1479318</v>
+        <v>63762.841725658829</v>
+      </c>
+      <c r="E259" s="26">
+        <v>1498081.4727735079</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
@@ -4993,10 +5020,10 @@
         <v>15</v>
       </c>
       <c r="D260" s="7">
-        <v>66892.326000000001</v>
-      </c>
-      <c r="E260" s="10">
-        <v>1571607</v>
+        <v>67439.561725658816</v>
+      </c>
+      <c r="E260" s="26">
+        <v>1584464.4814899988</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
@@ -5010,10 +5037,10 @@
         <v>16</v>
       </c>
       <c r="D261" s="7">
-        <v>66802.853000000003</v>
-      </c>
-      <c r="E261" s="10">
-        <v>1569505</v>
+        <v>67664.351725658824</v>
+      </c>
+      <c r="E261" s="26">
+        <v>1589745.8291393656</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
@@ -5027,10 +5054,10 @@
         <v>17</v>
       </c>
       <c r="D262" s="7">
-        <v>63998.012999999999</v>
-      </c>
-      <c r="E262" s="10">
-        <v>1503607</v>
+        <v>68359.702725658819</v>
+      </c>
+      <c r="E262" s="26">
+        <v>1606082.8119648243</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
@@ -5044,10 +5071,10 @@
         <v>18</v>
       </c>
       <c r="D263" s="7">
-        <v>64268.156999999999</v>
-      </c>
-      <c r="E263" s="10">
-        <v>1509954</v>
+        <v>65007.458725658827</v>
+      </c>
+      <c r="E263" s="26">
+        <v>1527323.2320479953</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
@@ -5061,10 +5088,10 @@
         <v>19</v>
       </c>
       <c r="D264" s="7">
-        <v>52338.826999999997</v>
-      </c>
-      <c r="E264" s="10">
-        <v>1229679</v>
+        <v>50313.723663944831</v>
+      </c>
+      <c r="E264" s="26">
+        <v>1182100.0320453169</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
@@ -5078,10 +5105,10 @@
         <v>20</v>
       </c>
       <c r="D265" s="7">
-        <v>43133.237000000001</v>
-      </c>
-      <c r="E265" s="10">
-        <v>1013397</v>
+        <v>47425.893259772834</v>
+      </c>
+      <c r="E265" s="26">
+        <v>1114251.6565978157</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
@@ -5095,10 +5122,10 @@
         <v>21</v>
       </c>
       <c r="D266" s="7">
-        <v>63825.440999999999</v>
-      </c>
-      <c r="E266" s="10">
-        <v>1499552</v>
+        <v>64564.742725658827</v>
+      </c>
+      <c r="E266" s="26">
+        <v>1516921.8035772578</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
@@ -5112,10 +5139,10 @@
         <v>22</v>
       </c>
       <c r="D267" s="7">
-        <v>68143.004000000001</v>
-      </c>
-      <c r="E267" s="10">
-        <v>1600992</v>
+        <v>67882.305725658822</v>
+      </c>
+      <c r="E267" s="26">
+        <v>1594866.5678091021</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
@@ -5129,10 +5156,10 @@
         <v>23</v>
       </c>
       <c r="D268" s="7">
-        <v>66613.365000000005</v>
-      </c>
-      <c r="E268" s="10">
-        <v>1565053</v>
+        <v>67352.666725658826</v>
+      </c>
+      <c r="E268" s="26">
+        <v>1582422.9195700213</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
@@ -5146,10 +5173,10 @@
         <v>24</v>
       </c>
       <c r="D269" s="7">
-        <v>44844.684999999998</v>
-      </c>
-      <c r="E269" s="10">
-        <v>1053607</v>
+        <v>43235.731815455481</v>
+      </c>
+      <c r="E269" s="26">
+        <v>1015805.5544828954</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
@@ -5163,10 +5190,10 @@
         <v>25</v>
       </c>
       <c r="D270" s="7">
-        <v>34447.531000000003</v>
-      </c>
-      <c r="E270" s="10">
-        <v>809330</v>
+        <v>38710.731815455481</v>
+      </c>
+      <c r="E270" s="26">
+        <v>909492.55962820945</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
@@ -5180,10 +5207,10 @@
         <v>26</v>
       </c>
       <c r="D271" s="7">
-        <v>54199.270000000004</v>
-      </c>
-      <c r="E271" s="10">
-        <v>1273389</v>
+        <v>42143.436451764595</v>
+      </c>
+      <c r="E271" s="26">
+        <v>990142.52876358794</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
@@ -5197,10 +5224,10 @@
         <v>27</v>
       </c>
       <c r="D272" s="7">
-        <v>45912.767</v>
-      </c>
-      <c r="E272" s="10">
-        <v>1078701</v>
+        <v>41177.027179146367</v>
+      </c>
+      <c r="E272" s="26">
+        <v>967437.14444814424</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
@@ -5214,10 +5241,10 @@
         <v>28</v>
       </c>
       <c r="D273" s="7">
-        <v>64601.021000000001</v>
-      </c>
-      <c r="E273" s="10">
-        <v>1517774</v>
+        <v>58471.830254307722</v>
+      </c>
+      <c r="E273" s="26">
+        <v>1373771.3566785168</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
@@ -5231,10 +5258,10 @@
         <v>29</v>
       </c>
       <c r="D274" s="7">
-        <v>67161.824999999997</v>
-      </c>
-      <c r="E274" s="10">
-        <v>1577939</v>
+        <v>68886.271975658819</v>
+      </c>
+      <c r="E274" s="28">
+        <v>1618454.3377031416</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
@@ -5248,10 +5275,10 @@
         <v>30</v>
       </c>
       <c r="D275" s="7">
-        <v>66898.096000000005</v>
-      </c>
-      <c r="E275" s="10">
-        <v>1571743</v>
+        <v>67637.397725658826</v>
+      </c>
+      <c r="E275" s="27">
+        <v>1589108.5561088</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
@@ -5265,10 +5292,10 @@
         <v>1</v>
       </c>
       <c r="D276" s="7">
-        <v>79113.032000000007</v>
-      </c>
-      <c r="E276" s="10">
-        <v>1858728</v>
+        <v>72084.645291818437</v>
+      </c>
+      <c r="E276" s="26">
+        <v>1693598.7898366801</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
@@ -5282,10 +5309,10 @@
         <v>2</v>
       </c>
       <c r="D277" s="7">
-        <v>76730.820000000007</v>
-      </c>
-      <c r="E277" s="10">
-        <v>1802759</v>
+        <v>70608.50696301843</v>
+      </c>
+      <c r="E277" s="26">
+        <v>1658917.5331395443</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
@@ -5299,10 +5326,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="7">
-        <v>62434.957000000002</v>
-      </c>
-      <c r="E278" s="10">
-        <v>1466883</v>
+        <v>56624.590499350939</v>
+      </c>
+      <c r="E278" s="26">
+        <v>1330371.2261671156</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
@@ -5316,10 +5343,10 @@
         <v>4</v>
       </c>
       <c r="D279" s="7">
-        <v>49654.921999999999</v>
-      </c>
-      <c r="E279" s="10">
-        <v>1166622</v>
+        <v>52156.985298870335</v>
+      </c>
+      <c r="E279" s="26">
+        <v>1225406.6982794993</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
@@ -5333,10 +5360,10 @@
         <v>5</v>
       </c>
       <c r="D280" s="7">
-        <v>42162.173999999999</v>
-      </c>
-      <c r="E280" s="10">
-        <v>990583</v>
+        <v>50123.166557233984</v>
+      </c>
+      <c r="E280" s="26">
+        <v>1177622.9719999526</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
@@ -5350,10 +5377,10 @@
         <v>6</v>
       </c>
       <c r="D281" s="7">
-        <v>67988.623999999996</v>
-      </c>
-      <c r="E281" s="10">
-        <v>1597364</v>
+        <v>76425.59818212493</v>
+      </c>
+      <c r="E281" s="26">
+        <v>1795587.6743210047</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
@@ -5367,10 +5394,10 @@
         <v>7</v>
       </c>
       <c r="D282" s="7">
-        <v>76949.760999999999</v>
-      </c>
-      <c r="E282" s="10">
-        <v>1807903</v>
+        <v>80765.575791818424</v>
+      </c>
+      <c r="E282" s="26">
+        <v>1897553.644992562</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
@@ -5384,10 +5411,10 @@
         <v>8</v>
       </c>
       <c r="D283" s="7">
-        <v>84182.357000000004</v>
-      </c>
-      <c r="E283" s="10">
-        <v>1977829</v>
+        <v>81263.583231818426</v>
+      </c>
+      <c r="E283" s="26">
+        <v>1909254.1228724108</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
@@ -5401,10 +5428,10 @@
         <v>9</v>
       </c>
       <c r="D284" s="7">
-        <v>62602.758000000002</v>
-      </c>
-      <c r="E284" s="10">
-        <v>1470826</v>
+        <v>60403.641229215857</v>
+      </c>
+      <c r="E284" s="26">
+        <v>1419158.4528631878</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
@@ -5418,10 +5445,10 @@
         <v>10</v>
       </c>
       <c r="D285" s="7">
-        <v>64410.033000000003</v>
-      </c>
-      <c r="E285" s="10">
-        <v>1513287</v>
+        <v>58721.068204215851</v>
+      </c>
+      <c r="E285" s="26">
+        <v>1379627.0987528099</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
@@ -5435,10 +5462,10 @@
         <v>11</v>
       </c>
       <c r="D286" s="7">
-        <v>57728.462</v>
-      </c>
-      <c r="E286" s="10">
-        <v>1356306</v>
+        <v>55282.863755584673</v>
+      </c>
+      <c r="E286" s="26">
+        <v>1298847.913812106</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
@@ -5452,10 +5479,10 @@
         <v>12</v>
       </c>
       <c r="D287" s="7">
-        <v>78306.494999999995</v>
-      </c>
-      <c r="E287" s="10">
-        <v>1839779</v>
+        <v>78755.015511818419</v>
+      </c>
+      <c r="E287" s="26">
+        <v>1850316.3666052304</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
@@ -5469,10 +5496,10 @@
         <v>13</v>
       </c>
       <c r="D288" s="7">
-        <v>81697.074000000008</v>
-      </c>
-      <c r="E288" s="10">
-        <v>1919439</v>
+        <v>85037.397408382923</v>
+      </c>
+      <c r="E288" s="26">
+        <v>1997918.3189244866</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
@@ -5486,10 +5513,10 @@
         <v>14</v>
       </c>
       <c r="D289" s="7">
-        <v>84070.979000000007</v>
-      </c>
-      <c r="E289" s="10">
-        <v>1975213</v>
+        <v>85586.825177182924</v>
+      </c>
+      <c r="E289" s="26">
+        <v>2010826.8960642559</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
@@ -5503,10 +5530,10 @@
         <v>15</v>
       </c>
       <c r="D290" s="7">
-        <v>84984.608000000007</v>
-      </c>
-      <c r="E290" s="10">
-        <v>1996678</v>
+        <v>85484.910228382912</v>
+      </c>
+      <c r="E290" s="26">
+        <v>2008432.4466880367</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
@@ -5520,10 +5547,10 @@
         <v>16</v>
       </c>
       <c r="D291" s="7">
-        <v>86243.358999999997</v>
-      </c>
-      <c r="E291" s="10">
-        <v>2026252</v>
+        <v>83733.436351818425</v>
+      </c>
+      <c r="E291" s="26">
+        <v>1967282.2956985745</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
@@ -5537,10 +5564,10 @@
         <v>17</v>
       </c>
       <c r="D292" s="7">
-        <v>75116.312999999995</v>
-      </c>
-      <c r="E292" s="10">
-        <v>1764827</v>
+        <v>74062.507251818417</v>
+      </c>
+      <c r="E292" s="26">
+        <v>1740067.8347818155</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
@@ -5554,10 +5581,10 @@
         <v>18</v>
       </c>
       <c r="D293" s="7">
-        <v>65153.313000000002</v>
-      </c>
-      <c r="E293" s="10">
-        <v>1530750</v>
+        <v>67104.15977181842</v>
+      </c>
+      <c r="E293" s="26">
+        <v>1576584.3519446095</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.3">
@@ -5571,10 +5598,10 @@
         <v>19</v>
       </c>
       <c r="D294" s="7">
-        <v>87998.773000000001</v>
-      </c>
-      <c r="E294" s="10">
-        <v>2067495</v>
+        <v>88447.293511818425</v>
+      </c>
+      <c r="E294" s="26">
+        <v>2078032.411056984</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
@@ -5588,10 +5615,10 @@
         <v>20</v>
       </c>
       <c r="D295" s="7">
-        <v>91008.059000000008</v>
-      </c>
-      <c r="E295" s="10">
-        <v>2138197</v>
+        <v>94554.59081680543</v>
+      </c>
+      <c r="E295" s="26">
+        <v>2221520.8236450772</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
@@ -5605,10 +5632,10 @@
         <v>21</v>
       </c>
       <c r="D296" s="7">
-        <v>85620.339000000007</v>
-      </c>
-      <c r="E296" s="10">
-        <v>2011614</v>
+        <v>96370.885431818431</v>
+      </c>
+      <c r="E296" s="26">
+        <v>2264193.9109512586</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
@@ -5622,10 +5649,10 @@
         <v>22</v>
       </c>
       <c r="D297" s="7">
-        <v>99008.572</v>
-      </c>
-      <c r="E297" s="10">
-        <v>2326165</v>
+        <v>95495.55427181843</v>
+      </c>
+      <c r="E297" s="26">
+        <v>2243628.3690486671</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
@@ -5639,10 +5666,10 @@
         <v>23</v>
       </c>
       <c r="D298" s="7">
-        <v>98889.036000000007</v>
-      </c>
-      <c r="E298" s="10">
-        <v>2323357</v>
+        <v>92445.469871818437</v>
+      </c>
+      <c r="E298" s="26">
+        <v>2171967.9033860024</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
@@ -5656,10 +5683,10 @@
         <v>24</v>
       </c>
       <c r="D299" s="7">
-        <v>81870.536000000007</v>
-      </c>
-      <c r="E299" s="10">
-        <v>1923514</v>
+        <v>82319.056511818431</v>
+      </c>
+      <c r="E299" s="26">
+        <v>1934052.0290350404</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
@@ -5673,10 +5700,10 @@
         <v>25</v>
       </c>
       <c r="D300" s="7">
-        <v>78991.184000000008</v>
-      </c>
-      <c r="E300" s="10">
-        <v>1855865</v>
+        <v>76389.503624259029</v>
+      </c>
+      <c r="E300" s="26">
+        <v>1794739.6476812963</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
@@ -5690,10 +5717,10 @@
         <v>26</v>
       </c>
       <c r="D301" s="7">
-        <v>104920.798</v>
-      </c>
-      <c r="E301" s="10">
-        <v>2465071</v>
+        <v>103017.5692155811</v>
+      </c>
+      <c r="E301" s="26">
+        <v>2420354.9847421725</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
@@ -5707,10 +5734,10 @@
         <v>27</v>
       </c>
       <c r="D302" s="7">
-        <v>108590.787</v>
-      </c>
-      <c r="E302" s="10">
-        <v>2551295</v>
+        <v>107734.60685438971</v>
+      </c>
+      <c r="E302" s="26">
+        <v>2531179.8241286967</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
@@ -5724,10 +5751,10 @@
         <v>28</v>
       </c>
       <c r="D303" s="7">
-        <v>98127.627999999997</v>
-      </c>
-      <c r="E303" s="10">
-        <v>2305468</v>
+        <v>112819.66301375782</v>
+      </c>
+      <c r="E303" s="26">
+        <v>2650651.1057434347</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.3">
@@ -5741,10 +5768,10 @@
         <v>29</v>
       </c>
       <c r="D304" s="7">
-        <v>120010.10400000001</v>
-      </c>
-      <c r="E304" s="10">
-        <v>2819588</v>
+        <v>111799.40010188789</v>
+      </c>
+      <c r="E304" s="26">
+        <v>2626680.4525500527</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.3">
@@ -5758,10 +5785,10 @@
         <v>30</v>
       </c>
       <c r="D305" s="7">
-        <v>128875.342</v>
-      </c>
-      <c r="E305" s="10">
-        <v>3027873</v>
+        <v>107677.73812265295</v>
+      </c>
+      <c r="E305" s="26">
+        <v>2529843.7169055976</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.3">
@@ -5775,10 +5802,10 @@
         <v>31</v>
       </c>
       <c r="D306" s="7">
-        <v>70957.960000000006</v>
-      </c>
-      <c r="E306" s="10">
-        <v>1667128</v>
+        <v>91103.35094528136</v>
+      </c>
+      <c r="E306" s="27">
+        <v>2140438.1768597499</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.3">
@@ -5794,7 +5821,7 @@
       <c r="D307" s="7">
         <v>70154.569000000003</v>
       </c>
-      <c r="E307" s="10">
+      <c r="E307" s="24">
         <v>1648252</v>
       </c>
     </row>
@@ -5811,7 +5838,7 @@
       <c r="D308" s="7">
         <v>94612.235000000001</v>
       </c>
-      <c r="E308" s="10">
+      <c r="E308" s="24">
         <v>2222875</v>
       </c>
     </row>
@@ -5828,7 +5855,7 @@
       <c r="D309" s="7">
         <v>109602.216</v>
       </c>
-      <c r="E309" s="10">
+      <c r="E309" s="24">
         <v>2575059</v>
       </c>
     </row>
@@ -5845,7 +5872,7 @@
       <c r="D310" s="7">
         <v>114272.39</v>
       </c>
-      <c r="E310" s="10">
+      <c r="E310" s="24">
         <v>2684782</v>
       </c>
     </row>
@@ -5862,7 +5889,7 @@
       <c r="D311" s="7">
         <v>113044.734</v>
       </c>
-      <c r="E311" s="10">
+      <c r="E311" s="24">
         <v>2655939</v>
       </c>
     </row>
@@ -5879,7 +5906,7 @@
       <c r="D312" s="7">
         <v>96006.692999999999</v>
       </c>
-      <c r="E312" s="10">
+      <c r="E312" s="24">
         <v>2255637</v>
       </c>
     </row>
@@ -5896,7 +5923,7 @@
       <c r="D313" s="7">
         <v>78949.903999999995</v>
       </c>
-      <c r="E313" s="10">
+      <c r="E313" s="24">
         <v>1854895</v>
       </c>
     </row>
@@ -5913,7 +5940,7 @@
       <c r="D314" s="7">
         <v>117192.984</v>
       </c>
-      <c r="E314" s="10">
+      <c r="E314" s="24">
         <v>2753400</v>
       </c>
     </row>
@@ -5930,7 +5957,7 @@
       <c r="D315" s="7">
         <v>138771.239</v>
       </c>
-      <c r="E315" s="10">
+      <c r="E315" s="24">
         <v>3260373</v>
       </c>
     </row>
@@ -5947,7 +5974,7 @@
       <c r="D316" s="7">
         <v>139233.98199999999</v>
       </c>
-      <c r="E316" s="10">
+      <c r="E316" s="24">
         <v>3271245</v>
       </c>
     </row>
@@ -5964,7 +5991,7 @@
       <c r="D317" s="7">
         <v>115765.97900000001</v>
       </c>
-      <c r="E317" s="10">
+      <c r="E317" s="24">
         <v>2719874</v>
       </c>
     </row>
@@ -5981,7 +6008,7 @@
       <c r="D318" s="7">
         <v>113775.939</v>
       </c>
-      <c r="E318" s="10">
+      <c r="E318" s="24">
         <v>2673118</v>
       </c>
     </row>
@@ -5998,7 +6025,7 @@
       <c r="D319" s="7">
         <v>121383.448</v>
       </c>
-      <c r="E319" s="10">
+      <c r="E319" s="24">
         <v>2851854</v>
       </c>
     </row>
@@ -6015,7 +6042,7 @@
       <c r="D320" s="7">
         <v>115552.493</v>
       </c>
-      <c r="E320" s="10">
+      <c r="E320" s="24">
         <v>2714858</v>
       </c>
     </row>
@@ -6032,7 +6059,7 @@
       <c r="D321" s="7">
         <v>128137.895</v>
       </c>
-      <c r="E321" s="10">
+      <c r="E321" s="24">
         <v>3010547</v>
       </c>
     </row>
@@ -6049,7 +6076,7 @@
       <c r="D322" s="7">
         <v>158549.421</v>
       </c>
-      <c r="E322" s="10">
+      <c r="E322" s="24">
         <v>3725053</v>
       </c>
     </row>
@@ -6066,7 +6093,7 @@
       <c r="D323" s="7">
         <v>165313.79</v>
       </c>
-      <c r="E323" s="10">
+      <c r="E323" s="24">
         <v>3883979</v>
       </c>
     </row>
@@ -6083,7 +6110,7 @@
       <c r="D324" s="7">
         <v>160874.12100000001</v>
       </c>
-      <c r="E324" s="10">
+      <c r="E324" s="24">
         <v>3779671</v>
       </c>
     </row>
@@ -6098,9 +6125,9 @@
         <v>19</v>
       </c>
       <c r="D325" s="7">
-        <v>164234.66700000002</v>
-      </c>
-      <c r="E325" s="10">
+        <v>164234.66699999999</v>
+      </c>
+      <c r="E325" s="24">
         <v>3858625</v>
       </c>
     </row>
@@ -6117,7 +6144,7 @@
       <c r="D326" s="7">
         <v>144378.31400000001</v>
       </c>
-      <c r="E326" s="10">
+      <c r="E326" s="24">
         <v>3392108</v>
       </c>
     </row>
@@ -6134,7 +6161,7 @@
       <c r="D327" s="7">
         <v>136447.25099999999</v>
       </c>
-      <c r="E327" s="10">
+      <c r="E327" s="24">
         <v>3205771</v>
       </c>
     </row>
@@ -6151,7 +6178,7 @@
       <c r="D328" s="7">
         <v>156470.55600000001</v>
       </c>
-      <c r="E328" s="10">
+      <c r="E328" s="24">
         <v>3676211</v>
       </c>
     </row>
@@ -6166,9 +6193,9 @@
         <v>23</v>
       </c>
       <c r="D329" s="7">
-        <v>167913.89800000002</v>
-      </c>
-      <c r="E329" s="10">
+        <v>167913.89799999999</v>
+      </c>
+      <c r="E329" s="24">
         <v>3945067</v>
       </c>
     </row>
@@ -6185,7 +6212,7 @@
       <c r="D330" s="7">
         <v>177827.17800000001</v>
       </c>
-      <c r="E330" s="10">
+      <c r="E330" s="24">
         <v>4177976</v>
       </c>
     </row>
@@ -6202,7 +6229,7 @@
       <c r="D331" s="7">
         <v>179767.103</v>
       </c>
-      <c r="E331" s="10">
+      <c r="E331" s="24">
         <v>4223553</v>
       </c>
     </row>
@@ -6219,7 +6246,7 @@
       <c r="D332" s="7">
         <v>173801.674</v>
       </c>
-      <c r="E332" s="10">
+      <c r="E332" s="24">
         <v>4083398</v>
       </c>
     </row>
@@ -6236,7 +6263,7 @@
       <c r="D333" s="7">
         <v>167382.94500000001</v>
       </c>
-      <c r="E333" s="10">
+      <c r="E333" s="24">
         <v>3932593</v>
       </c>
     </row>
@@ -6253,7 +6280,7 @@
       <c r="D334" s="7">
         <v>168289.394</v>
       </c>
-      <c r="E334" s="10">
+      <c r="E334" s="24">
         <v>3953889</v>
       </c>
     </row>
@@ -6270,7 +6297,7 @@
       <c r="D335" s="7">
         <v>117989.001</v>
       </c>
-      <c r="E335" s="10">
+      <c r="E335" s="24">
         <v>2772103</v>
       </c>
     </row>
@@ -6287,7 +6314,7 @@
       <c r="D336" s="7">
         <v>139961.69899999999</v>
       </c>
-      <c r="E336" s="10">
+      <c r="E336" s="24">
         <v>3288342</v>
       </c>
     </row>
@@ -6304,7 +6331,7 @@
       <c r="D337" s="7">
         <v>195160.715</v>
       </c>
-      <c r="E337" s="10">
+      <c r="E337" s="24">
         <v>4585220</v>
       </c>
     </row>
@@ -6321,7 +6348,7 @@
       <c r="D338" s="7">
         <v>203831.32</v>
       </c>
-      <c r="E338" s="10">
+      <c r="E338" s="24">
         <v>4788932</v>
       </c>
     </row>
@@ -6338,7 +6365,7 @@
       <c r="D339" s="7">
         <v>199600.755</v>
       </c>
-      <c r="E339" s="10">
+      <c r="E339" s="24">
         <v>4689537</v>
       </c>
     </row>
@@ -6355,7 +6382,7 @@
       <c r="D340" s="7">
         <v>215681.12100000001</v>
       </c>
-      <c r="E340" s="10">
+      <c r="E340" s="24">
         <v>5067338</v>
       </c>
     </row>
@@ -6372,7 +6399,7 @@
       <c r="D341" s="7">
         <v>202047.25599999999</v>
       </c>
-      <c r="E341" s="10">
+      <c r="E341" s="24">
         <v>4747016</v>
       </c>
     </row>
@@ -6387,9 +6414,9 @@
         <v>6</v>
       </c>
       <c r="D342" s="7">
-        <v>170776.55000000002</v>
-      </c>
-      <c r="E342" s="10">
+        <v>170776.55</v>
+      </c>
+      <c r="E342" s="24">
         <v>4012324</v>
       </c>
     </row>
@@ -6406,7 +6433,7 @@
       <c r="D343" s="7">
         <v>187429.42300000001</v>
       </c>
-      <c r="E343" s="10">
+      <c r="E343" s="24">
         <v>4403576</v>
       </c>
     </row>
@@ -6423,7 +6450,7 @@
       <c r="D344" s="7">
         <v>192216.302</v>
       </c>
-      <c r="E344" s="10">
+      <c r="E344" s="24">
         <v>4516042</v>
       </c>
     </row>
@@ -6440,7 +6467,7 @@
       <c r="D345" s="7">
         <v>193439.34</v>
       </c>
-      <c r="E345" s="10">
+      <c r="E345" s="24">
         <v>4544777</v>
       </c>
     </row>
@@ -6457,7 +6484,7 @@
       <c r="D346" s="7">
         <v>199522.429</v>
       </c>
-      <c r="E346" s="10">
+      <c r="E346" s="24">
         <v>4687697</v>
       </c>
     </row>
@@ -6474,7 +6501,7 @@
       <c r="D347" s="7">
         <v>206188.95600000001</v>
       </c>
-      <c r="E347" s="10">
+      <c r="E347" s="24">
         <v>4844324</v>
       </c>
     </row>
@@ -6491,7 +6518,7 @@
       <c r="D348" s="7">
         <v>181086.59700000001</v>
       </c>
-      <c r="E348" s="10">
+      <c r="E348" s="24">
         <v>4254554</v>
       </c>
     </row>
@@ -6508,7 +6535,7 @@
       <c r="D349" s="7">
         <v>167668.84</v>
       </c>
-      <c r="E349" s="10">
+      <c r="E349" s="24">
         <v>3939310</v>
       </c>
     </row>
@@ -6525,7 +6552,7 @@
       <c r="D350" s="7">
         <v>188892.43</v>
       </c>
-      <c r="E350" s="10">
+      <c r="E350" s="24">
         <v>4437949</v>
       </c>
     </row>
@@ -6542,41 +6569,41 @@
       <c r="D351" s="7">
         <v>246799.66200000001</v>
       </c>
-      <c r="E351" s="10">
+      <c r="E351" s="24">
         <v>5798456</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A352" s="17">
-        <v>2026</v>
-      </c>
-      <c r="B352" s="17">
+      <c r="A352" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B352" s="16">
         <v>12</v>
       </c>
-      <c r="C352" s="17">
+      <c r="C352" s="16">
         <v>16</v>
       </c>
-      <c r="D352" s="18">
+      <c r="D352" s="17">
         <v>263079.32400000002</v>
       </c>
-      <c r="E352" s="19">
+      <c r="E352" s="24">
         <v>6180939</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A353" s="17">
-        <v>2026</v>
-      </c>
-      <c r="B353" s="17">
+      <c r="A353" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B353" s="16">
         <v>12</v>
       </c>
-      <c r="C353" s="17">
+      <c r="C353" s="16">
         <v>17</v>
       </c>
-      <c r="D353" s="18">
-        <v>281382.03500000003</v>
-      </c>
-      <c r="E353" s="19">
+      <c r="D353" s="17">
+        <v>281382.03499999997</v>
+      </c>
+      <c r="E353" s="24">
         <v>6610954</v>
       </c>
     </row>
@@ -6593,7 +6620,7 @@
       <c r="D354" s="7">
         <v>210288.63</v>
       </c>
-      <c r="E354" s="10">
+      <c r="E354" s="24">
         <v>4940644</v>
       </c>
     </row>
@@ -6610,7 +6637,7 @@
       <c r="D355" s="7">
         <v>217441.75599999999</v>
       </c>
-      <c r="E355" s="10">
+      <c r="E355" s="24">
         <v>5108704</v>
       </c>
     </row>
@@ -6627,7 +6654,7 @@
       <c r="D356" s="7">
         <v>228900.73800000001</v>
       </c>
-      <c r="E356" s="10">
+      <c r="E356" s="24">
         <v>5377928</v>
       </c>
     </row>
@@ -6644,7 +6671,7 @@
       <c r="D357" s="7">
         <v>251888.182</v>
       </c>
-      <c r="E357" s="10">
+      <c r="E357" s="24">
         <v>5918008</v>
       </c>
     </row>
@@ -6661,7 +6688,7 @@
       <c r="D358" s="7">
         <v>250442.196</v>
       </c>
-      <c r="E358" s="10">
+      <c r="E358" s="24">
         <v>5884035</v>
       </c>
     </row>
@@ -6678,7 +6705,7 @@
       <c r="D359" s="7">
         <v>235607.516</v>
       </c>
-      <c r="E359" s="10">
+      <c r="E359" s="24">
         <v>5535501</v>
       </c>
     </row>
@@ -6695,7 +6722,7 @@
       <c r="D360" s="7">
         <v>233756.64600000001</v>
       </c>
-      <c r="E360" s="10">
+      <c r="E360" s="24">
         <v>5492015</v>
       </c>
     </row>
@@ -6712,24 +6739,24 @@
       <c r="D361" s="7">
         <v>209953.06700000001</v>
       </c>
-      <c r="E361" s="10">
+      <c r="E361" s="24">
         <v>4932760</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A362" s="17">
-        <v>2026</v>
-      </c>
-      <c r="B362" s="17">
+      <c r="A362" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B362" s="16">
         <v>12</v>
       </c>
-      <c r="C362" s="17">
+      <c r="C362" s="16">
         <v>26</v>
       </c>
-      <c r="D362" s="18">
+      <c r="D362" s="17">
         <v>265474.79100000003</v>
       </c>
-      <c r="E362" s="19">
+      <c r="E362" s="24">
         <v>6237220</v>
       </c>
     </row>
@@ -6746,7 +6773,7 @@
       <c r="D363" s="7">
         <v>246228.00599999999</v>
       </c>
-      <c r="E363" s="10">
+      <c r="E363" s="24">
         <v>5785025</v>
       </c>
     </row>
@@ -6763,7 +6790,7 @@
       <c r="D364" s="7">
         <v>249009.236</v>
       </c>
-      <c r="E364" s="10">
+      <c r="E364" s="24">
         <v>5850369</v>
       </c>
     </row>
@@ -6780,7 +6807,7 @@
       <c r="D365" s="7">
         <v>222771.052</v>
       </c>
-      <c r="E365" s="10">
+      <c r="E365" s="24">
         <v>5233913</v>
       </c>
     </row>
@@ -6797,7 +6824,7 @@
       <c r="D366" s="7">
         <v>222329.641</v>
       </c>
-      <c r="E366" s="10">
+      <c r="E366" s="24">
         <v>5223543</v>
       </c>
     </row>
@@ -6812,9 +6839,9 @@
         <v>31</v>
       </c>
       <c r="D367" s="9">
-        <v>228565.46600000001</v>
-      </c>
-      <c r="E367" s="11">
+        <v>228565.46599999999</v>
+      </c>
+      <c r="E367" s="24">
         <v>5370051</v>
       </c>
     </row>
